--- a/log.xlsx
+++ b/log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3982,6 +3982,4038 @@
         <v>1.7</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L74" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="L76" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>7</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>7</v>
+      </c>
+      <c r="L77" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L78" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G79" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L79" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G80" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L80" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E81" t="n">
+        <v>25</v>
+      </c>
+      <c r="F81" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J81" t="n">
+        <v>25</v>
+      </c>
+      <c r="K81" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L81" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="D82" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="E82" t="n">
+        <v>176</v>
+      </c>
+      <c r="F82" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G82" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H82" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="I82" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J82" t="n">
+        <v>176</v>
+      </c>
+      <c r="K82" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L82" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="D83" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="E83" t="n">
+        <v>382</v>
+      </c>
+      <c r="F83" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G83" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H83" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="I83" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="J83" t="n">
+        <v>382</v>
+      </c>
+      <c r="K83" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L83" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="D84" t="n">
+        <v>93.61</v>
+      </c>
+      <c r="E84" t="n">
+        <v>577</v>
+      </c>
+      <c r="F84" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G84" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H84" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="I84" t="n">
+        <v>93.61</v>
+      </c>
+      <c r="J84" t="n">
+        <v>577</v>
+      </c>
+      <c r="K84" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L84" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="D85" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="E85" t="n">
+        <v>734</v>
+      </c>
+      <c r="F85" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G85" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H85" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="I85" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="J85" t="n">
+        <v>734</v>
+      </c>
+      <c r="K85" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="L85" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>63.73</v>
+      </c>
+      <c r="D86" t="n">
+        <v>214.23</v>
+      </c>
+      <c r="E86" t="n">
+        <v>838</v>
+      </c>
+      <c r="F86" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="G86" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H86" t="n">
+        <v>63.73</v>
+      </c>
+      <c r="I86" t="n">
+        <v>214.23</v>
+      </c>
+      <c r="J86" t="n">
+        <v>838</v>
+      </c>
+      <c r="K86" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L86" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>65.65000000000001</v>
+      </c>
+      <c r="D87" t="n">
+        <v>279.88</v>
+      </c>
+      <c r="E87" t="n">
+        <v>872</v>
+      </c>
+      <c r="F87" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H87" t="n">
+        <v>65.65000000000001</v>
+      </c>
+      <c r="I87" t="n">
+        <v>279.88</v>
+      </c>
+      <c r="J87" t="n">
+        <v>872</v>
+      </c>
+      <c r="K87" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="L87" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="D88" t="n">
+        <v>343.08</v>
+      </c>
+      <c r="E88" t="n">
+        <v>839</v>
+      </c>
+      <c r="F88" t="n">
+        <v>18</v>
+      </c>
+      <c r="G88" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H88" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="I88" t="n">
+        <v>343.08</v>
+      </c>
+      <c r="J88" t="n">
+        <v>839</v>
+      </c>
+      <c r="K88" t="n">
+        <v>18</v>
+      </c>
+      <c r="L88" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="D89" t="n">
+        <v>399.57</v>
+      </c>
+      <c r="E89" t="n">
+        <v>740</v>
+      </c>
+      <c r="F89" t="n">
+        <v>18</v>
+      </c>
+      <c r="G89" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H89" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="I89" t="n">
+        <v>399.57</v>
+      </c>
+      <c r="J89" t="n">
+        <v>740</v>
+      </c>
+      <c r="K89" t="n">
+        <v>18</v>
+      </c>
+      <c r="L89" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="D90" t="n">
+        <v>445.31</v>
+      </c>
+      <c r="E90" t="n">
+        <v>588</v>
+      </c>
+      <c r="F90" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G90" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="H90" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="I90" t="n">
+        <v>445.31</v>
+      </c>
+      <c r="J90" t="n">
+        <v>588</v>
+      </c>
+      <c r="K90" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="L90" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="D91" t="n">
+        <v>477.06</v>
+      </c>
+      <c r="E91" t="n">
+        <v>397</v>
+      </c>
+      <c r="F91" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G91" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="H91" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="I91" t="n">
+        <v>477.06</v>
+      </c>
+      <c r="J91" t="n">
+        <v>397</v>
+      </c>
+      <c r="K91" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="L91" t="n">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D92" t="n">
+        <v>492.56</v>
+      </c>
+      <c r="E92" t="n">
+        <v>190</v>
+      </c>
+      <c r="F92" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="G92" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H92" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="I92" t="n">
+        <v>492.56</v>
+      </c>
+      <c r="J92" t="n">
+        <v>190</v>
+      </c>
+      <c r="K92" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="L92" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="D93" t="n">
+        <v>495.09</v>
+      </c>
+      <c r="E93" t="n">
+        <v>31</v>
+      </c>
+      <c r="F93" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G93" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I93" t="n">
+        <v>495.09</v>
+      </c>
+      <c r="J93" t="n">
+        <v>31</v>
+      </c>
+      <c r="K93" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L93" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>495.09</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G94" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>495.09</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L94" t="n">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>495.09</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>495.09</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L95" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>495.09</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G96" t="n">
+        <v>8</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>495.09</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L96" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>495.09</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G97" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>495.09</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L97" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G98" t="n">
+        <v>17</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L98" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G99" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="L99" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G100" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="L100" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G101" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L101" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L102" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G103" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L103" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L104" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="E105" t="n">
+        <v>24</v>
+      </c>
+      <c r="F105" t="n">
+        <v>6</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J105" t="n">
+        <v>24</v>
+      </c>
+      <c r="K105" t="n">
+        <v>6</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="D106" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="E106" t="n">
+        <v>127</v>
+      </c>
+      <c r="F106" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H106" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="I106" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="J106" t="n">
+        <v>127</v>
+      </c>
+      <c r="K106" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="L106" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="D107" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="E107" t="n">
+        <v>323</v>
+      </c>
+      <c r="F107" t="n">
+        <v>9</v>
+      </c>
+      <c r="G107" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H107" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="I107" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="J107" t="n">
+        <v>323</v>
+      </c>
+      <c r="K107" t="n">
+        <v>9</v>
+      </c>
+      <c r="L107" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>47.01</v>
+      </c>
+      <c r="D108" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="E108" t="n">
+        <v>586</v>
+      </c>
+      <c r="F108" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G108" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H108" t="n">
+        <v>47.01</v>
+      </c>
+      <c r="I108" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="J108" t="n">
+        <v>586</v>
+      </c>
+      <c r="K108" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L108" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>58.73</v>
+      </c>
+      <c r="D109" t="n">
+        <v>144.42</v>
+      </c>
+      <c r="E109" t="n">
+        <v>753</v>
+      </c>
+      <c r="F109" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G109" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H109" t="n">
+        <v>58.73</v>
+      </c>
+      <c r="I109" t="n">
+        <v>144.42</v>
+      </c>
+      <c r="J109" t="n">
+        <v>753</v>
+      </c>
+      <c r="K109" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L109" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>54.56</v>
+      </c>
+      <c r="D110" t="n">
+        <v>198.98</v>
+      </c>
+      <c r="E110" t="n">
+        <v>696</v>
+      </c>
+      <c r="F110" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G110" t="n">
+        <v>8</v>
+      </c>
+      <c r="H110" t="n">
+        <v>54.56</v>
+      </c>
+      <c r="I110" t="n">
+        <v>198.98</v>
+      </c>
+      <c r="J110" t="n">
+        <v>696</v>
+      </c>
+      <c r="K110" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="L110" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>66.92</v>
+      </c>
+      <c r="D111" t="n">
+        <v>265.9</v>
+      </c>
+      <c r="E111" t="n">
+        <v>879</v>
+      </c>
+      <c r="F111" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G111" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H111" t="n">
+        <v>66.92</v>
+      </c>
+      <c r="I111" t="n">
+        <v>265.9</v>
+      </c>
+      <c r="J111" t="n">
+        <v>879</v>
+      </c>
+      <c r="K111" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="L111" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>59.44</v>
+      </c>
+      <c r="D112" t="n">
+        <v>325.34</v>
+      </c>
+      <c r="E112" t="n">
+        <v>771</v>
+      </c>
+      <c r="F112" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="G112" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H112" t="n">
+        <v>59.44</v>
+      </c>
+      <c r="I112" t="n">
+        <v>325.34</v>
+      </c>
+      <c r="J112" t="n">
+        <v>771</v>
+      </c>
+      <c r="K112" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="L112" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>54.43</v>
+      </c>
+      <c r="D113" t="n">
+        <v>379.77</v>
+      </c>
+      <c r="E113" t="n">
+        <v>701</v>
+      </c>
+      <c r="F113" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G113" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H113" t="n">
+        <v>54.43</v>
+      </c>
+      <c r="I113" t="n">
+        <v>379.77</v>
+      </c>
+      <c r="J113" t="n">
+        <v>701</v>
+      </c>
+      <c r="K113" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="L113" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="D114" t="n">
+        <v>426.07</v>
+      </c>
+      <c r="E114" t="n">
+        <v>588</v>
+      </c>
+      <c r="F114" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="G114" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H114" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="I114" t="n">
+        <v>426.07</v>
+      </c>
+      <c r="J114" t="n">
+        <v>588</v>
+      </c>
+      <c r="K114" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="L114" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="D115" t="n">
+        <v>458.31</v>
+      </c>
+      <c r="E115" t="n">
+        <v>398</v>
+      </c>
+      <c r="F115" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G115" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H115" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="I115" t="n">
+        <v>458.31</v>
+      </c>
+      <c r="J115" t="n">
+        <v>398</v>
+      </c>
+      <c r="K115" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="L115" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="D116" t="n">
+        <v>474.22</v>
+      </c>
+      <c r="E116" t="n">
+        <v>195</v>
+      </c>
+      <c r="F116" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G116" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H116" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="I116" t="n">
+        <v>474.22</v>
+      </c>
+      <c r="J116" t="n">
+        <v>195</v>
+      </c>
+      <c r="K116" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="L116" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="D117" t="n">
+        <v>476.99</v>
+      </c>
+      <c r="E117" t="n">
+        <v>34</v>
+      </c>
+      <c r="F117" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G117" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H117" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="I117" t="n">
+        <v>476.99</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34</v>
+      </c>
+      <c r="K117" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L117" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="n">
+        <v>476.99</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G118" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>476.99</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L118" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" t="n">
+        <v>476.99</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="G119" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>476.99</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L119" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>476.99</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>9</v>
+      </c>
+      <c r="G120" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>476.99</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>9</v>
+      </c>
+      <c r="L120" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>476.99</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G121" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>476.99</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L121" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G122" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="L122" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G123" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L123" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G124" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L124" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G125" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L125" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G126" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L126" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G127" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L127" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G128" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L128" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E129" t="n">
+        <v>22</v>
+      </c>
+      <c r="F129" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G129" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J129" t="n">
+        <v>22</v>
+      </c>
+      <c r="K129" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L129" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="D130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E130" t="n">
+        <v>114</v>
+      </c>
+      <c r="F130" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="G130" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H130" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J130" t="n">
+        <v>114</v>
+      </c>
+      <c r="K130" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L130" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>28.23</v>
+      </c>
+      <c r="D131" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="E131" t="n">
+        <v>346</v>
+      </c>
+      <c r="F131" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H131" t="n">
+        <v>28.23</v>
+      </c>
+      <c r="I131" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="J131" t="n">
+        <v>346</v>
+      </c>
+      <c r="K131" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L131" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="D132" t="n">
+        <v>84.97</v>
+      </c>
+      <c r="E132" t="n">
+        <v>578</v>
+      </c>
+      <c r="F132" t="n">
+        <v>15</v>
+      </c>
+      <c r="G132" t="n">
+        <v>6</v>
+      </c>
+      <c r="H132" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="I132" t="n">
+        <v>84.97</v>
+      </c>
+      <c r="J132" t="n">
+        <v>578</v>
+      </c>
+      <c r="K132" t="n">
+        <v>15</v>
+      </c>
+      <c r="L132" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="D133" t="n">
+        <v>139.55</v>
+      </c>
+      <c r="E133" t="n">
+        <v>706</v>
+      </c>
+      <c r="F133" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G133" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H133" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="I133" t="n">
+        <v>139.55</v>
+      </c>
+      <c r="J133" t="n">
+        <v>706</v>
+      </c>
+      <c r="K133" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="L133" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>59.49</v>
+      </c>
+      <c r="D134" t="n">
+        <v>199.04</v>
+      </c>
+      <c r="E134" t="n">
+        <v>779</v>
+      </c>
+      <c r="F134" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G134" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H134" t="n">
+        <v>59.49</v>
+      </c>
+      <c r="I134" t="n">
+        <v>199.04</v>
+      </c>
+      <c r="J134" t="n">
+        <v>779</v>
+      </c>
+      <c r="K134" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="L134" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>63.19</v>
+      </c>
+      <c r="D135" t="n">
+        <v>262.23</v>
+      </c>
+      <c r="E135" t="n">
+        <v>836</v>
+      </c>
+      <c r="F135" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G135" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H135" t="n">
+        <v>63.19</v>
+      </c>
+      <c r="I135" t="n">
+        <v>262.23</v>
+      </c>
+      <c r="J135" t="n">
+        <v>836</v>
+      </c>
+      <c r="K135" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="L135" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>60.91</v>
+      </c>
+      <c r="D136" t="n">
+        <v>323.14</v>
+      </c>
+      <c r="E136" t="n">
+        <v>803</v>
+      </c>
+      <c r="F136" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G136" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H136" t="n">
+        <v>60.91</v>
+      </c>
+      <c r="I136" t="n">
+        <v>323.14</v>
+      </c>
+      <c r="J136" t="n">
+        <v>803</v>
+      </c>
+      <c r="K136" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="L136" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="D137" t="n">
+        <v>361.29</v>
+      </c>
+      <c r="E137" t="n">
+        <v>480</v>
+      </c>
+      <c r="F137" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G137" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H137" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="I137" t="n">
+        <v>361.29</v>
+      </c>
+      <c r="J137" t="n">
+        <v>480</v>
+      </c>
+      <c r="K137" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="L137" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="D138" t="n">
+        <v>387.08</v>
+      </c>
+      <c r="E138" t="n">
+        <v>316</v>
+      </c>
+      <c r="F138" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G138" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H138" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="I138" t="n">
+        <v>387.08</v>
+      </c>
+      <c r="J138" t="n">
+        <v>316</v>
+      </c>
+      <c r="K138" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="L138" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="D139" t="n">
+        <v>400.22</v>
+      </c>
+      <c r="E139" t="n">
+        <v>161</v>
+      </c>
+      <c r="F139" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="G139" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H139" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="I139" t="n">
+        <v>400.22</v>
+      </c>
+      <c r="J139" t="n">
+        <v>161</v>
+      </c>
+      <c r="K139" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="L139" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="D140" t="n">
+        <v>404.3</v>
+      </c>
+      <c r="E140" t="n">
+        <v>50</v>
+      </c>
+      <c r="F140" t="n">
+        <v>13</v>
+      </c>
+      <c r="G140" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H140" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="I140" t="n">
+        <v>404.3</v>
+      </c>
+      <c r="J140" t="n">
+        <v>50</v>
+      </c>
+      <c r="K140" t="n">
+        <v>13</v>
+      </c>
+      <c r="L140" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D141" t="n">
+        <v>404.95</v>
+      </c>
+      <c r="E141" t="n">
+        <v>8</v>
+      </c>
+      <c r="F141" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G141" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I141" t="n">
+        <v>404.95</v>
+      </c>
+      <c r="J141" t="n">
+        <v>8</v>
+      </c>
+      <c r="K141" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L141" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>404.95</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="G142" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>404.95</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="L142" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>404.95</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G143" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>404.95</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L143" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="n">
+        <v>404.95</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G144" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>404.95</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="L144" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>404.95</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G145" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>404.95</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L145" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G146" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="L146" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="n">
+        <v>10</v>
+      </c>
+      <c r="G147" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>10</v>
+      </c>
+      <c r="L147" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G148" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L148" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G149" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="L149" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G150" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L150" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G151" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L151" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G152" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L152" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E153" t="n">
+        <v>4</v>
+      </c>
+      <c r="F153" t="n">
+        <v>12</v>
+      </c>
+      <c r="G153" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J153" t="n">
+        <v>4</v>
+      </c>
+      <c r="K153" t="n">
+        <v>12</v>
+      </c>
+      <c r="L153" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E154" t="n">
+        <v>7</v>
+      </c>
+      <c r="F154" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G154" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J154" t="n">
+        <v>7</v>
+      </c>
+      <c r="K154" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="L154" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="D155" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E155" t="n">
+        <v>16</v>
+      </c>
+      <c r="F155" t="n">
+        <v>11</v>
+      </c>
+      <c r="G155" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H155" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I155" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="J155" t="n">
+        <v>16</v>
+      </c>
+      <c r="K155" t="n">
+        <v>11</v>
+      </c>
+      <c r="L155" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="D156" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="E156" t="n">
+        <v>158</v>
+      </c>
+      <c r="F156" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G156" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H156" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="I156" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="J156" t="n">
+        <v>158</v>
+      </c>
+      <c r="K156" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L156" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="D157" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="E157" t="n">
+        <v>232</v>
+      </c>
+      <c r="F157" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G157" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H157" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="I157" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="J157" t="n">
+        <v>232</v>
+      </c>
+      <c r="K157" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="L157" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D158" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="E158" t="n">
+        <v>212</v>
+      </c>
+      <c r="F158" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G158" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H158" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="I158" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="J158" t="n">
+        <v>212</v>
+      </c>
+      <c r="K158" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="L158" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="D159" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="E159" t="n">
+        <v>396</v>
+      </c>
+      <c r="F159" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G159" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H159" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="I159" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="J159" t="n">
+        <v>396</v>
+      </c>
+      <c r="K159" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="L159" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="D160" t="n">
+        <v>137.2</v>
+      </c>
+      <c r="E160" t="n">
+        <v>705</v>
+      </c>
+      <c r="F160" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G160" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H160" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="I160" t="n">
+        <v>137.2</v>
+      </c>
+      <c r="J160" t="n">
+        <v>705</v>
+      </c>
+      <c r="K160" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L160" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="D161" t="n">
+        <v>173.25</v>
+      </c>
+      <c r="E161" t="n">
+        <v>453</v>
+      </c>
+      <c r="F161" t="n">
+        <v>17</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H161" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="I161" t="n">
+        <v>173.25</v>
+      </c>
+      <c r="J161" t="n">
+        <v>453</v>
+      </c>
+      <c r="K161" t="n">
+        <v>17</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D162" t="n">
+        <v>200.05</v>
+      </c>
+      <c r="E162" t="n">
+        <v>333</v>
+      </c>
+      <c r="F162" t="n">
+        <v>18</v>
+      </c>
+      <c r="G162" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H162" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="I162" t="n">
+        <v>200.05</v>
+      </c>
+      <c r="J162" t="n">
+        <v>333</v>
+      </c>
+      <c r="K162" t="n">
+        <v>18</v>
+      </c>
+      <c r="L162" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="D163" t="n">
+        <v>227.64</v>
+      </c>
+      <c r="E163" t="n">
+        <v>343</v>
+      </c>
+      <c r="F163" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G163" t="n">
+        <v>15</v>
+      </c>
+      <c r="H163" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="I163" t="n">
+        <v>227.64</v>
+      </c>
+      <c r="J163" t="n">
+        <v>343</v>
+      </c>
+      <c r="K163" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L163" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="D164" t="n">
+        <v>241.92</v>
+      </c>
+      <c r="E164" t="n">
+        <v>175</v>
+      </c>
+      <c r="F164" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="G164" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H164" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="I164" t="n">
+        <v>241.92</v>
+      </c>
+      <c r="J164" t="n">
+        <v>175</v>
+      </c>
+      <c r="K164" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="L164" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="D165" t="n">
+        <v>244.45</v>
+      </c>
+      <c r="E165" t="n">
+        <v>31</v>
+      </c>
+      <c r="F165" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G165" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H165" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I165" t="n">
+        <v>244.45</v>
+      </c>
+      <c r="J165" t="n">
+        <v>31</v>
+      </c>
+      <c r="K165" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="L165" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>244.45</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" t="n">
+        <v>11</v>
+      </c>
+      <c r="G166" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>244.45</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>11</v>
+      </c>
+      <c r="L166" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" t="n">
+        <v>244.45</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G167" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" t="n">
+        <v>244.45</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L167" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" t="n">
+        <v>244.45</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G168" t="n">
+        <v>17</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>244.45</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L168" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="n">
+        <v>244.45</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G169" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" t="n">
+        <v>244.45</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L169" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/log.xlsx
+++ b/log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L410"/>
+  <dimension ref="A1:L577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18102,23 +18102,7052 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>0</v>
+      </c>
+      <c r="D410" t="n">
+        <v>0</v>
+      </c>
+      <c r="E410" t="n">
+        <v>0</v>
+      </c>
+      <c r="F410" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G410" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H410" t="n">
+        <v>0</v>
+      </c>
+      <c r="I410" t="n">
+        <v>0</v>
+      </c>
+      <c r="J410" t="n">
+        <v>0</v>
+      </c>
+      <c r="K410" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L410" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>0</v>
+      </c>
+      <c r="D411" t="n">
+        <v>0</v>
+      </c>
+      <c r="E411" t="n">
+        <v>0</v>
+      </c>
+      <c r="F411" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="G411" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H411" t="n">
+        <v>0</v>
+      </c>
+      <c r="I411" t="n">
+        <v>0</v>
+      </c>
+      <c r="J411" t="n">
+        <v>0</v>
+      </c>
+      <c r="K411" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="L411" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>0</v>
+      </c>
+      <c r="D412" t="n">
+        <v>0</v>
+      </c>
+      <c r="E412" t="n">
+        <v>0</v>
+      </c>
+      <c r="F412" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G412" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H412" t="n">
+        <v>0</v>
+      </c>
+      <c r="I412" t="n">
+        <v>0</v>
+      </c>
+      <c r="J412" t="n">
+        <v>0</v>
+      </c>
+      <c r="K412" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="L412" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>0</v>
+      </c>
+      <c r="D413" t="n">
+        <v>0</v>
+      </c>
+      <c r="E413" t="n">
+        <v>0</v>
+      </c>
+      <c r="F413" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G413" t="n">
+        <v>14</v>
+      </c>
+      <c r="H413" t="n">
+        <v>0</v>
+      </c>
+      <c r="I413" t="n">
+        <v>0</v>
+      </c>
+      <c r="J413" t="n">
+        <v>0</v>
+      </c>
+      <c r="K413" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L413" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>0</v>
+      </c>
+      <c r="D414" t="n">
+        <v>0</v>
+      </c>
+      <c r="E414" t="n">
+        <v>0</v>
+      </c>
+      <c r="F414" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G414" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H414" t="n">
+        <v>0</v>
+      </c>
+      <c r="I414" t="n">
+        <v>0</v>
+      </c>
+      <c r="J414" t="n">
+        <v>0</v>
+      </c>
+      <c r="K414" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L414" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>0</v>
+      </c>
+      <c r="D415" t="n">
+        <v>0</v>
+      </c>
+      <c r="E415" t="n">
+        <v>0</v>
+      </c>
+      <c r="F415" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G415" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H415" t="n">
+        <v>0</v>
+      </c>
+      <c r="I415" t="n">
+        <v>0</v>
+      </c>
+      <c r="J415" t="n">
+        <v>0</v>
+      </c>
+      <c r="K415" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L415" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>0</v>
+      </c>
+      <c r="D416" t="n">
+        <v>0</v>
+      </c>
+      <c r="E416" t="n">
+        <v>0</v>
+      </c>
+      <c r="F416" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G416" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H416" t="n">
+        <v>0</v>
+      </c>
+      <c r="I416" t="n">
+        <v>0</v>
+      </c>
+      <c r="J416" t="n">
+        <v>0</v>
+      </c>
+      <c r="K416" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L416" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="D417" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="E417" t="n">
+        <v>57</v>
+      </c>
+      <c r="F417" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G417" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H417" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="I417" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="J417" t="n">
+        <v>57</v>
+      </c>
+      <c r="K417" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="L417" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="D418" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="E418" t="n">
+        <v>234</v>
+      </c>
+      <c r="F418" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G418" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H418" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="I418" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="J418" t="n">
+        <v>234</v>
+      </c>
+      <c r="K418" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L418" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>35.73</v>
+      </c>
+      <c r="D419" t="n">
+        <v>59.47</v>
+      </c>
+      <c r="E419" t="n">
+        <v>442</v>
+      </c>
+      <c r="F419" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G419" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H419" t="n">
+        <v>35.73</v>
+      </c>
+      <c r="I419" t="n">
+        <v>59.47</v>
+      </c>
+      <c r="J419" t="n">
+        <v>442</v>
+      </c>
+      <c r="K419" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L419" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
           <t>10시</t>
         </is>
       </c>
-      <c r="C410" t="n">
+      <c r="C420" t="n">
+        <v>49.69</v>
+      </c>
+      <c r="D420" t="n">
+        <v>109.16</v>
+      </c>
+      <c r="E420" t="n">
+        <v>635</v>
+      </c>
+      <c r="F420" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="G420" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H420" t="n">
+        <v>49.69</v>
+      </c>
+      <c r="I420" t="n">
+        <v>109.16</v>
+      </c>
+      <c r="J420" t="n">
+        <v>635</v>
+      </c>
+      <c r="K420" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="L420" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="D421" t="n">
+        <v>169.06</v>
+      </c>
+      <c r="E421" t="n">
+        <v>785</v>
+      </c>
+      <c r="F421" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G421" t="n">
+        <v>16</v>
+      </c>
+      <c r="H421" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I421" t="n">
+        <v>169.06</v>
+      </c>
+      <c r="J421" t="n">
+        <v>785</v>
+      </c>
+      <c r="K421" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="L421" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="D422" t="n">
+        <v>234.81</v>
+      </c>
+      <c r="E422" t="n">
+        <v>877</v>
+      </c>
+      <c r="F422" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="G422" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H422" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="I422" t="n">
+        <v>234.81</v>
+      </c>
+      <c r="J422" t="n">
+        <v>877</v>
+      </c>
+      <c r="K422" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="L422" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>67.31999999999999</v>
+      </c>
+      <c r="D423" t="n">
+        <v>302.13</v>
+      </c>
+      <c r="E423" t="n">
+        <v>904</v>
+      </c>
+      <c r="F423" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G423" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H423" t="n">
+        <v>67.31999999999999</v>
+      </c>
+      <c r="I423" t="n">
+        <v>302.13</v>
+      </c>
+      <c r="J423" t="n">
+        <v>904</v>
+      </c>
+      <c r="K423" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L423" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>64.65000000000001</v>
+      </c>
+      <c r="D424" t="n">
+        <v>366.78</v>
+      </c>
+      <c r="E424" t="n">
+        <v>865</v>
+      </c>
+      <c r="F424" t="n">
+        <v>19</v>
+      </c>
+      <c r="G424" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H424" t="n">
+        <v>64.65000000000001</v>
+      </c>
+      <c r="I424" t="n">
+        <v>366.78</v>
+      </c>
+      <c r="J424" t="n">
+        <v>865</v>
+      </c>
+      <c r="K424" t="n">
+        <v>19</v>
+      </c>
+      <c r="L424" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
         <v>58.2</v>
       </c>
-      <c r="D410" t="n">
-        <v>12340.5</v>
-      </c>
-      <c r="E410" t="n">
-        <v>650.3</v>
-      </c>
-      <c r="F410" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="G410" t="n">
+      <c r="D425" t="n">
+        <v>424.98</v>
+      </c>
+      <c r="E425" t="n">
+        <v>772</v>
+      </c>
+      <c r="F425" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="G425" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H425" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="I425" t="n">
+        <v>424.98</v>
+      </c>
+      <c r="J425" t="n">
+        <v>772</v>
+      </c>
+      <c r="K425" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="L425" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="D426" t="n">
+        <v>472.6</v>
+      </c>
+      <c r="E426" t="n">
+        <v>618</v>
+      </c>
+      <c r="F426" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G426" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="H426" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="I426" t="n">
+        <v>472.6</v>
+      </c>
+      <c r="J426" t="n">
+        <v>618</v>
+      </c>
+      <c r="K426" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="L426" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>33.79</v>
+      </c>
+      <c r="D427" t="n">
+        <v>506.39</v>
+      </c>
+      <c r="E427" t="n">
+        <v>425</v>
+      </c>
+      <c r="F427" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G427" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H427" t="n">
+        <v>33.79</v>
+      </c>
+      <c r="I427" t="n">
+        <v>506.39</v>
+      </c>
+      <c r="J427" t="n">
+        <v>425</v>
+      </c>
+      <c r="K427" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="L427" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="D428" t="n">
+        <v>524.1799999999999</v>
+      </c>
+      <c r="E428" t="n">
+        <v>218</v>
+      </c>
+      <c r="F428" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="G428" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H428" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="I428" t="n">
+        <v>524.1799999999999</v>
+      </c>
+      <c r="J428" t="n">
+        <v>218</v>
+      </c>
+      <c r="K428" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="L428" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D429" t="n">
+        <v>528.1</v>
+      </c>
+      <c r="E429" t="n">
+        <v>48</v>
+      </c>
+      <c r="F429" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G429" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H429" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="I429" t="n">
+        <v>528.1</v>
+      </c>
+      <c r="J429" t="n">
+        <v>48</v>
+      </c>
+      <c r="K429" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="L429" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>0</v>
+      </c>
+      <c r="D430" t="n">
+        <v>528.1</v>
+      </c>
+      <c r="E430" t="n">
+        <v>0</v>
+      </c>
+      <c r="F430" t="n">
+        <v>12</v>
+      </c>
+      <c r="G430" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H430" t="n">
+        <v>0</v>
+      </c>
+      <c r="I430" t="n">
+        <v>528.1</v>
+      </c>
+      <c r="J430" t="n">
+        <v>0</v>
+      </c>
+      <c r="K430" t="n">
+        <v>12</v>
+      </c>
+      <c r="L430" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>0</v>
+      </c>
+      <c r="D431" t="n">
+        <v>528.1</v>
+      </c>
+      <c r="E431" t="n">
+        <v>0</v>
+      </c>
+      <c r="F431" t="n">
+        <v>11</v>
+      </c>
+      <c r="G431" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H431" t="n">
+        <v>0</v>
+      </c>
+      <c r="I431" t="n">
+        <v>528.1</v>
+      </c>
+      <c r="J431" t="n">
+        <v>0</v>
+      </c>
+      <c r="K431" t="n">
+        <v>11</v>
+      </c>
+      <c r="L431" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>0</v>
+      </c>
+      <c r="D432" t="n">
+        <v>528.1</v>
+      </c>
+      <c r="E432" t="n">
+        <v>0</v>
+      </c>
+      <c r="F432" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G432" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0</v>
+      </c>
+      <c r="I432" t="n">
+        <v>528.1</v>
+      </c>
+      <c r="J432" t="n">
+        <v>0</v>
+      </c>
+      <c r="K432" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L432" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>0</v>
+      </c>
+      <c r="D433" t="n">
+        <v>528.1</v>
+      </c>
+      <c r="E433" t="n">
+        <v>0</v>
+      </c>
+      <c r="F433" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G433" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0</v>
+      </c>
+      <c r="I433" t="n">
+        <v>528.1</v>
+      </c>
+      <c r="J433" t="n">
+        <v>0</v>
+      </c>
+      <c r="K433" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L433" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>0</v>
+      </c>
+      <c r="D434" t="n">
+        <v>0</v>
+      </c>
+      <c r="E434" t="n">
+        <v>0</v>
+      </c>
+      <c r="F434" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G434" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0</v>
+      </c>
+      <c r="I434" t="n">
+        <v>0</v>
+      </c>
+      <c r="J434" t="n">
+        <v>0</v>
+      </c>
+      <c r="K434" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L434" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>0</v>
+      </c>
+      <c r="D435" t="n">
+        <v>0</v>
+      </c>
+      <c r="E435" t="n">
+        <v>0</v>
+      </c>
+      <c r="F435" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G435" t="n">
+        <v>7</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0</v>
+      </c>
+      <c r="I435" t="n">
+        <v>0</v>
+      </c>
+      <c r="J435" t="n">
+        <v>0</v>
+      </c>
+      <c r="K435" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L435" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>0</v>
+      </c>
+      <c r="D436" t="n">
+        <v>0</v>
+      </c>
+      <c r="E436" t="n">
+        <v>0</v>
+      </c>
+      <c r="F436" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G436" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0</v>
+      </c>
+      <c r="I436" t="n">
+        <v>0</v>
+      </c>
+      <c r="J436" t="n">
+        <v>0</v>
+      </c>
+      <c r="K436" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L436" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>0</v>
+      </c>
+      <c r="D437" t="n">
+        <v>0</v>
+      </c>
+      <c r="E437" t="n">
+        <v>0</v>
+      </c>
+      <c r="F437" t="n">
+        <v>10</v>
+      </c>
+      <c r="G437" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H437" t="n">
+        <v>0</v>
+      </c>
+      <c r="I437" t="n">
+        <v>0</v>
+      </c>
+      <c r="J437" t="n">
+        <v>0</v>
+      </c>
+      <c r="K437" t="n">
+        <v>10</v>
+      </c>
+      <c r="L437" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>0</v>
+      </c>
+      <c r="D438" t="n">
+        <v>0</v>
+      </c>
+      <c r="E438" t="n">
+        <v>0</v>
+      </c>
+      <c r="F438" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G438" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0</v>
+      </c>
+      <c r="I438" t="n">
+        <v>0</v>
+      </c>
+      <c r="J438" t="n">
+        <v>0</v>
+      </c>
+      <c r="K438" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L438" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>0</v>
+      </c>
+      <c r="D439" t="n">
+        <v>0</v>
+      </c>
+      <c r="E439" t="n">
+        <v>0</v>
+      </c>
+      <c r="F439" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G439" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0</v>
+      </c>
+      <c r="I439" t="n">
+        <v>0</v>
+      </c>
+      <c r="J439" t="n">
+        <v>0</v>
+      </c>
+      <c r="K439" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L439" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>0</v>
+      </c>
+      <c r="D440" t="n">
+        <v>0</v>
+      </c>
+      <c r="E440" t="n">
+        <v>0</v>
+      </c>
+      <c r="F440" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G440" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0</v>
+      </c>
+      <c r="I440" t="n">
+        <v>0</v>
+      </c>
+      <c r="J440" t="n">
+        <v>0</v>
+      </c>
+      <c r="K440" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L440" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D441" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E441" t="n">
+        <v>15</v>
+      </c>
+      <c r="F441" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G441" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H441" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I441" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J441" t="n">
+        <v>15</v>
+      </c>
+      <c r="K441" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L441" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="D442" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="E442" t="n">
+        <v>89</v>
+      </c>
+      <c r="F442" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G442" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H442" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="I442" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="J442" t="n">
+        <v>89</v>
+      </c>
+      <c r="K442" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L442" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="D443" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="E443" t="n">
+        <v>109</v>
+      </c>
+      <c r="F443" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G443" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H443" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="I443" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="J443" t="n">
+        <v>109</v>
+      </c>
+      <c r="K443" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L443" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="D444" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="E444" t="n">
+        <v>105</v>
+      </c>
+      <c r="F444" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G444" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H444" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="I444" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="J444" t="n">
+        <v>105</v>
+      </c>
+      <c r="K444" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="L444" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="D445" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="E445" t="n">
+        <v>307</v>
+      </c>
+      <c r="F445" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G445" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H445" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="I445" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="J445" t="n">
+        <v>307</v>
+      </c>
+      <c r="K445" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="L445" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="D446" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="E446" t="n">
+        <v>320</v>
+      </c>
+      <c r="F446" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G446" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H446" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="I446" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="J446" t="n">
+        <v>320</v>
+      </c>
+      <c r="K446" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="L446" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>31.07</v>
+      </c>
+      <c r="D447" t="n">
+        <v>108.17</v>
+      </c>
+      <c r="E447" t="n">
+        <v>383</v>
+      </c>
+      <c r="F447" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G447" t="n">
+        <v>3</v>
+      </c>
+      <c r="H447" t="n">
+        <v>31.07</v>
+      </c>
+      <c r="I447" t="n">
+        <v>108.17</v>
+      </c>
+      <c r="J447" t="n">
+        <v>383</v>
+      </c>
+      <c r="K447" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="L447" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="D448" t="n">
+        <v>140.47</v>
+      </c>
+      <c r="E448" t="n">
+        <v>401</v>
+      </c>
+      <c r="F448" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G448" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H448" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="I448" t="n">
+        <v>140.47</v>
+      </c>
+      <c r="J448" t="n">
+        <v>401</v>
+      </c>
+      <c r="K448" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="L448" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="D449" t="n">
+        <v>158.91</v>
+      </c>
+      <c r="E449" t="n">
+        <v>226</v>
+      </c>
+      <c r="F449" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G449" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H449" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="I449" t="n">
+        <v>158.91</v>
+      </c>
+      <c r="J449" t="n">
+        <v>226</v>
+      </c>
+      <c r="K449" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="L449" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="D450" t="n">
+        <v>174.25</v>
+      </c>
+      <c r="E450" t="n">
+        <v>188</v>
+      </c>
+      <c r="F450" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G450" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H450" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="I450" t="n">
+        <v>174.25</v>
+      </c>
+      <c r="J450" t="n">
+        <v>188</v>
+      </c>
+      <c r="K450" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="L450" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="D451" t="n">
+        <v>180.37</v>
+      </c>
+      <c r="E451" t="n">
+        <v>75</v>
+      </c>
+      <c r="F451" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G451" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H451" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="I451" t="n">
+        <v>180.37</v>
+      </c>
+      <c r="J451" t="n">
+        <v>75</v>
+      </c>
+      <c r="K451" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="L451" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="D452" t="n">
+        <v>185.92</v>
+      </c>
+      <c r="E452" t="n">
+        <v>68</v>
+      </c>
+      <c r="F452" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G452" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H452" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="I452" t="n">
+        <v>185.92</v>
+      </c>
+      <c r="J452" t="n">
+        <v>68</v>
+      </c>
+      <c r="K452" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L452" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D453" t="n">
+        <v>187.14</v>
+      </c>
+      <c r="E453" t="n">
+        <v>15</v>
+      </c>
+      <c r="F453" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="G453" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H453" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I453" t="n">
+        <v>187.14</v>
+      </c>
+      <c r="J453" t="n">
+        <v>15</v>
+      </c>
+      <c r="K453" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="L453" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>0</v>
+      </c>
+      <c r="D454" t="n">
+        <v>187.14</v>
+      </c>
+      <c r="E454" t="n">
+        <v>0</v>
+      </c>
+      <c r="F454" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G454" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H454" t="n">
+        <v>0</v>
+      </c>
+      <c r="I454" t="n">
+        <v>187.14</v>
+      </c>
+      <c r="J454" t="n">
+        <v>0</v>
+      </c>
+      <c r="K454" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="L454" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>0</v>
+      </c>
+      <c r="D455" t="n">
+        <v>187.14</v>
+      </c>
+      <c r="E455" t="n">
+        <v>0</v>
+      </c>
+      <c r="F455" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G455" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H455" t="n">
+        <v>0</v>
+      </c>
+      <c r="I455" t="n">
+        <v>187.14</v>
+      </c>
+      <c r="J455" t="n">
+        <v>0</v>
+      </c>
+      <c r="K455" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L455" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>0</v>
+      </c>
+      <c r="D456" t="n">
+        <v>187.14</v>
+      </c>
+      <c r="E456" t="n">
+        <v>0</v>
+      </c>
+      <c r="F456" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G456" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H456" t="n">
+        <v>0</v>
+      </c>
+      <c r="I456" t="n">
+        <v>187.14</v>
+      </c>
+      <c r="J456" t="n">
+        <v>0</v>
+      </c>
+      <c r="K456" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L456" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>0</v>
+      </c>
+      <c r="D457" t="n">
+        <v>187.14</v>
+      </c>
+      <c r="E457" t="n">
+        <v>0</v>
+      </c>
+      <c r="F457" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G457" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H457" t="n">
+        <v>0</v>
+      </c>
+      <c r="I457" t="n">
+        <v>187.14</v>
+      </c>
+      <c r="J457" t="n">
+        <v>0</v>
+      </c>
+      <c r="K457" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L457" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>0</v>
+      </c>
+      <c r="D458" t="n">
+        <v>0</v>
+      </c>
+      <c r="E458" t="n">
+        <v>0</v>
+      </c>
+      <c r="F458" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G458" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H458" t="n">
+        <v>0</v>
+      </c>
+      <c r="I458" t="n">
+        <v>0</v>
+      </c>
+      <c r="J458" t="n">
+        <v>0</v>
+      </c>
+      <c r="K458" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="L458" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>0</v>
+      </c>
+      <c r="D459" t="n">
+        <v>0</v>
+      </c>
+      <c r="E459" t="n">
+        <v>0</v>
+      </c>
+      <c r="F459" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G459" t="n">
+        <v>13</v>
+      </c>
+      <c r="H459" t="n">
+        <v>0</v>
+      </c>
+      <c r="I459" t="n">
+        <v>0</v>
+      </c>
+      <c r="J459" t="n">
+        <v>0</v>
+      </c>
+      <c r="K459" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="L459" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>0</v>
+      </c>
+      <c r="D460" t="n">
+        <v>0</v>
+      </c>
+      <c r="E460" t="n">
+        <v>0</v>
+      </c>
+      <c r="F460" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G460" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H460" t="n">
+        <v>0</v>
+      </c>
+      <c r="I460" t="n">
+        <v>0</v>
+      </c>
+      <c r="J460" t="n">
+        <v>0</v>
+      </c>
+      <c r="K460" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L460" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>0</v>
+      </c>
+      <c r="D461" t="n">
+        <v>0</v>
+      </c>
+      <c r="E461" t="n">
+        <v>0</v>
+      </c>
+      <c r="F461" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G461" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H461" t="n">
+        <v>0</v>
+      </c>
+      <c r="I461" t="n">
+        <v>0</v>
+      </c>
+      <c r="J461" t="n">
+        <v>0</v>
+      </c>
+      <c r="K461" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L461" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>0</v>
+      </c>
+      <c r="D462" t="n">
+        <v>0</v>
+      </c>
+      <c r="E462" t="n">
+        <v>0</v>
+      </c>
+      <c r="F462" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G462" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H462" t="n">
+        <v>0</v>
+      </c>
+      <c r="I462" t="n">
+        <v>0</v>
+      </c>
+      <c r="J462" t="n">
+        <v>0</v>
+      </c>
+      <c r="K462" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L462" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>0</v>
+      </c>
+      <c r="D463" t="n">
+        <v>0</v>
+      </c>
+      <c r="E463" t="n">
+        <v>0</v>
+      </c>
+      <c r="F463" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G463" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H463" t="n">
+        <v>0</v>
+      </c>
+      <c r="I463" t="n">
+        <v>0</v>
+      </c>
+      <c r="J463" t="n">
+        <v>0</v>
+      </c>
+      <c r="K463" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L463" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>0</v>
+      </c>
+      <c r="D464" t="n">
+        <v>0</v>
+      </c>
+      <c r="E464" t="n">
+        <v>0</v>
+      </c>
+      <c r="F464" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G464" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H464" t="n">
+        <v>0</v>
+      </c>
+      <c r="I464" t="n">
+        <v>0</v>
+      </c>
+      <c r="J464" t="n">
+        <v>0</v>
+      </c>
+      <c r="K464" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="L464" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="D465" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E465" t="n">
+        <v>17</v>
+      </c>
+      <c r="F465" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G465" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H465" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I465" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="J465" t="n">
+        <v>17</v>
+      </c>
+      <c r="K465" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L465" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="D466" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="E466" t="n">
+        <v>73</v>
+      </c>
+      <c r="F466" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G466" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H466" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="I466" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="J466" t="n">
+        <v>73</v>
+      </c>
+      <c r="K466" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="L466" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="D467" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="E467" t="n">
+        <v>90</v>
+      </c>
+      <c r="F467" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="G467" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H467" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="I467" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="J467" t="n">
+        <v>90</v>
+      </c>
+      <c r="K467" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="L467" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="D468" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="E468" t="n">
+        <v>291</v>
+      </c>
+      <c r="F468" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G468" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H468" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="I468" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="J468" t="n">
+        <v>291</v>
+      </c>
+      <c r="K468" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="L468" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="D469" t="n">
+        <v>88</v>
+      </c>
+      <c r="E469" t="n">
+        <v>641</v>
+      </c>
+      <c r="F469" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G469" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H469" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="I469" t="n">
+        <v>88</v>
+      </c>
+      <c r="J469" t="n">
+        <v>641</v>
+      </c>
+      <c r="K469" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="L469" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="D470" t="n">
+        <v>147.55</v>
+      </c>
+      <c r="E470" t="n">
+        <v>789</v>
+      </c>
+      <c r="F470" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G470" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H470" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="I470" t="n">
+        <v>147.55</v>
+      </c>
+      <c r="J470" t="n">
+        <v>789</v>
+      </c>
+      <c r="K470" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="L470" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>52.31</v>
+      </c>
+      <c r="D471" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="E471" t="n">
+        <v>683</v>
+      </c>
+      <c r="F471" t="n">
+        <v>19</v>
+      </c>
+      <c r="G471" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H471" t="n">
+        <v>52.31</v>
+      </c>
+      <c r="I471" t="n">
+        <v>199.86</v>
+      </c>
+      <c r="J471" t="n">
+        <v>683</v>
+      </c>
+      <c r="K471" t="n">
+        <v>19</v>
+      </c>
+      <c r="L471" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>53.91</v>
+      </c>
+      <c r="D472" t="n">
+        <v>253.77</v>
+      </c>
+      <c r="E472" t="n">
+        <v>708</v>
+      </c>
+      <c r="F472" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G472" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H472" t="n">
+        <v>53.91</v>
+      </c>
+      <c r="I472" t="n">
+        <v>253.77</v>
+      </c>
+      <c r="J472" t="n">
+        <v>708</v>
+      </c>
+      <c r="K472" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="L472" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="D473" t="n">
+        <v>290.45</v>
+      </c>
+      <c r="E473" t="n">
+        <v>466</v>
+      </c>
+      <c r="F473" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G473" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H473" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="I473" t="n">
+        <v>290.45</v>
+      </c>
+      <c r="J473" t="n">
+        <v>466</v>
+      </c>
+      <c r="K473" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="L473" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="D474" t="n">
+        <v>318.49</v>
+      </c>
+      <c r="E474" t="n">
+        <v>350</v>
+      </c>
+      <c r="F474" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G474" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H474" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="I474" t="n">
+        <v>318.49</v>
+      </c>
+      <c r="J474" t="n">
+        <v>350</v>
+      </c>
+      <c r="K474" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L474" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="D475" t="n">
+        <v>338.94</v>
+      </c>
+      <c r="E475" t="n">
+        <v>251</v>
+      </c>
+      <c r="F475" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G475" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H475" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="I475" t="n">
+        <v>338.94</v>
+      </c>
+      <c r="J475" t="n">
+        <v>251</v>
+      </c>
+      <c r="K475" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="L475" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="D476" t="n">
+        <v>350.28</v>
+      </c>
+      <c r="E476" t="n">
+        <v>139</v>
+      </c>
+      <c r="F476" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="G476" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H476" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="I476" t="n">
+        <v>350.28</v>
+      </c>
+      <c r="J476" t="n">
+        <v>139</v>
+      </c>
+      <c r="K476" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="L476" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="D477" t="n">
+        <v>352.32</v>
+      </c>
+      <c r="E477" t="n">
+        <v>25</v>
+      </c>
+      <c r="F477" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G477" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H477" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I477" t="n">
+        <v>352.32</v>
+      </c>
+      <c r="J477" t="n">
+        <v>25</v>
+      </c>
+      <c r="K477" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="L477" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>0</v>
+      </c>
+      <c r="D478" t="n">
+        <v>352.32</v>
+      </c>
+      <c r="E478" t="n">
+        <v>0</v>
+      </c>
+      <c r="F478" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G478" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H478" t="n">
+        <v>0</v>
+      </c>
+      <c r="I478" t="n">
+        <v>352.32</v>
+      </c>
+      <c r="J478" t="n">
+        <v>0</v>
+      </c>
+      <c r="K478" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L478" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>0</v>
+      </c>
+      <c r="D479" t="n">
+        <v>352.32</v>
+      </c>
+      <c r="E479" t="n">
+        <v>0</v>
+      </c>
+      <c r="F479" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G479" t="n">
+        <v>1</v>
+      </c>
+      <c r="H479" t="n">
+        <v>0</v>
+      </c>
+      <c r="I479" t="n">
+        <v>352.32</v>
+      </c>
+      <c r="J479" t="n">
+        <v>0</v>
+      </c>
+      <c r="K479" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="L479" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>0</v>
+      </c>
+      <c r="D480" t="n">
+        <v>352.32</v>
+      </c>
+      <c r="E480" t="n">
+        <v>0</v>
+      </c>
+      <c r="F480" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G480" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H480" t="n">
+        <v>0</v>
+      </c>
+      <c r="I480" t="n">
+        <v>352.32</v>
+      </c>
+      <c r="J480" t="n">
+        <v>0</v>
+      </c>
+      <c r="K480" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="L480" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>0</v>
+      </c>
+      <c r="D481" t="n">
+        <v>352.32</v>
+      </c>
+      <c r="E481" t="n">
+        <v>0</v>
+      </c>
+      <c r="F481" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G481" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H481" t="n">
+        <v>0</v>
+      </c>
+      <c r="I481" t="n">
+        <v>352.32</v>
+      </c>
+      <c r="J481" t="n">
+        <v>0</v>
+      </c>
+      <c r="K481" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="L481" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>0</v>
+      </c>
+      <c r="D482" t="n">
+        <v>0</v>
+      </c>
+      <c r="E482" t="n">
+        <v>0</v>
+      </c>
+      <c r="F482" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G482" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H482" t="n">
+        <v>0</v>
+      </c>
+      <c r="I482" t="n">
+        <v>0</v>
+      </c>
+      <c r="J482" t="n">
+        <v>0</v>
+      </c>
+      <c r="K482" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="L482" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>0</v>
+      </c>
+      <c r="D483" t="n">
+        <v>0</v>
+      </c>
+      <c r="E483" t="n">
+        <v>0</v>
+      </c>
+      <c r="F483" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G483" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H483" t="n">
+        <v>0</v>
+      </c>
+      <c r="I483" t="n">
+        <v>0</v>
+      </c>
+      <c r="J483" t="n">
+        <v>0</v>
+      </c>
+      <c r="K483" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L483" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>0</v>
+      </c>
+      <c r="D484" t="n">
+        <v>0</v>
+      </c>
+      <c r="E484" t="n">
+        <v>0</v>
+      </c>
+      <c r="F484" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G484" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H484" t="n">
+        <v>0</v>
+      </c>
+      <c r="I484" t="n">
+        <v>0</v>
+      </c>
+      <c r="J484" t="n">
+        <v>0</v>
+      </c>
+      <c r="K484" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L484" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>0</v>
+      </c>
+      <c r="D485" t="n">
+        <v>0</v>
+      </c>
+      <c r="E485" t="n">
+        <v>0</v>
+      </c>
+      <c r="F485" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G485" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H485" t="n">
+        <v>0</v>
+      </c>
+      <c r="I485" t="n">
+        <v>0</v>
+      </c>
+      <c r="J485" t="n">
+        <v>0</v>
+      </c>
+      <c r="K485" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="L485" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>0</v>
+      </c>
+      <c r="D486" t="n">
+        <v>0</v>
+      </c>
+      <c r="E486" t="n">
+        <v>0</v>
+      </c>
+      <c r="F486" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G486" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H486" t="n">
+        <v>0</v>
+      </c>
+      <c r="I486" t="n">
+        <v>0</v>
+      </c>
+      <c r="J486" t="n">
+        <v>0</v>
+      </c>
+      <c r="K486" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L486" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>0</v>
+      </c>
+      <c r="D487" t="n">
+        <v>0</v>
+      </c>
+      <c r="E487" t="n">
+        <v>0</v>
+      </c>
+      <c r="F487" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G487" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H487" t="n">
+        <v>0</v>
+      </c>
+      <c r="I487" t="n">
+        <v>0</v>
+      </c>
+      <c r="J487" t="n">
+        <v>0</v>
+      </c>
+      <c r="K487" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="L487" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>0</v>
+      </c>
+      <c r="D488" t="n">
+        <v>0</v>
+      </c>
+      <c r="E488" t="n">
+        <v>0</v>
+      </c>
+      <c r="F488" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G488" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H488" t="n">
+        <v>0</v>
+      </c>
+      <c r="I488" t="n">
+        <v>0</v>
+      </c>
+      <c r="J488" t="n">
+        <v>0</v>
+      </c>
+      <c r="K488" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="L488" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D489" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="E489" t="n">
+        <v>32</v>
+      </c>
+      <c r="F489" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="G489" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H489" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I489" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J489" t="n">
+        <v>32</v>
+      </c>
+      <c r="K489" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="L489" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="D490" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="E490" t="n">
+        <v>110</v>
+      </c>
+      <c r="F490" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="G490" t="n">
+        <v>7</v>
+      </c>
+      <c r="H490" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="I490" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="J490" t="n">
+        <v>110</v>
+      </c>
+      <c r="K490" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="L490" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="D491" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E491" t="n">
+        <v>157</v>
+      </c>
+      <c r="F491" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G491" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H491" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="I491" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="J491" t="n">
+        <v>157</v>
+      </c>
+      <c r="K491" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="L491" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="D492" t="n">
+        <v>60.04</v>
+      </c>
+      <c r="E492" t="n">
+        <v>451</v>
+      </c>
+      <c r="F492" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G492" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H492" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="I492" t="n">
+        <v>60.04</v>
+      </c>
+      <c r="J492" t="n">
+        <v>451</v>
+      </c>
+      <c r="K492" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="L492" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>34.21</v>
+      </c>
+      <c r="D493" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="E493" t="n">
+        <v>433</v>
+      </c>
+      <c r="F493" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="G493" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H493" t="n">
+        <v>34.21</v>
+      </c>
+      <c r="I493" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="J493" t="n">
+        <v>433</v>
+      </c>
+      <c r="K493" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="L493" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>40.37</v>
+      </c>
+      <c r="D494" t="n">
+        <v>134.62</v>
+      </c>
+      <c r="E494" t="n">
+        <v>516</v>
+      </c>
+      <c r="F494" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G494" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H494" t="n">
+        <v>40.37</v>
+      </c>
+      <c r="I494" t="n">
+        <v>134.62</v>
+      </c>
+      <c r="J494" t="n">
+        <v>516</v>
+      </c>
+      <c r="K494" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="L494" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>44.13</v>
+      </c>
+      <c r="D495" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="E495" t="n">
+        <v>570</v>
+      </c>
+      <c r="F495" t="n">
+        <v>20</v>
+      </c>
+      <c r="G495" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H495" t="n">
+        <v>44.13</v>
+      </c>
+      <c r="I495" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="J495" t="n">
+        <v>570</v>
+      </c>
+      <c r="K495" t="n">
+        <v>20</v>
+      </c>
+      <c r="L495" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="D496" t="n">
+        <v>231.53</v>
+      </c>
+      <c r="E496" t="n">
+        <v>696</v>
+      </c>
+      <c r="F496" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G496" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H496" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="I496" t="n">
+        <v>231.53</v>
+      </c>
+      <c r="J496" t="n">
+        <v>696</v>
+      </c>
+      <c r="K496" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="L496" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="D497" t="n">
+        <v>282.98</v>
+      </c>
+      <c r="E497" t="n">
+        <v>675</v>
+      </c>
+      <c r="F497" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="G497" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H497" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="I497" t="n">
+        <v>282.98</v>
+      </c>
+      <c r="J497" t="n">
+        <v>675</v>
+      </c>
+      <c r="K497" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="L497" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="D498" t="n">
+        <v>322.53</v>
+      </c>
+      <c r="E498" t="n">
+        <v>508</v>
+      </c>
+      <c r="F498" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="G498" t="n">
+        <v>9</v>
+      </c>
+      <c r="H498" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="I498" t="n">
+        <v>322.53</v>
+      </c>
+      <c r="J498" t="n">
+        <v>508</v>
+      </c>
+      <c r="K498" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="L498" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="D499" t="n">
+        <v>340.08</v>
+      </c>
+      <c r="E499" t="n">
+        <v>216</v>
+      </c>
+      <c r="F499" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G499" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H499" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="I499" t="n">
+        <v>340.08</v>
+      </c>
+      <c r="J499" t="n">
+        <v>216</v>
+      </c>
+      <c r="K499" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="L499" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="D500" t="n">
+        <v>347.83</v>
+      </c>
+      <c r="E500" t="n">
+        <v>95</v>
+      </c>
+      <c r="F500" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="G500" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H500" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="I500" t="n">
+        <v>347.83</v>
+      </c>
+      <c r="J500" t="n">
+        <v>95</v>
+      </c>
+      <c r="K500" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="L500" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="D501" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="E501" t="n">
+        <v>33</v>
+      </c>
+      <c r="F501" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G501" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H501" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="I501" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="J501" t="n">
+        <v>33</v>
+      </c>
+      <c r="K501" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="L501" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>0</v>
+      </c>
+      <c r="D502" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="E502" t="n">
+        <v>0</v>
+      </c>
+      <c r="F502" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G502" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H502" t="n">
+        <v>0</v>
+      </c>
+      <c r="I502" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="J502" t="n">
+        <v>0</v>
+      </c>
+      <c r="K502" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="L502" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>0</v>
+      </c>
+      <c r="D503" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="E503" t="n">
+        <v>0</v>
+      </c>
+      <c r="F503" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="G503" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H503" t="n">
+        <v>0</v>
+      </c>
+      <c r="I503" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="J503" t="n">
+        <v>0</v>
+      </c>
+      <c r="K503" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="L503" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>0</v>
+      </c>
+      <c r="D504" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="E504" t="n">
+        <v>0</v>
+      </c>
+      <c r="F504" t="n">
+        <v>14</v>
+      </c>
+      <c r="G504" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H504" t="n">
+        <v>0</v>
+      </c>
+      <c r="I504" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="J504" t="n">
+        <v>0</v>
+      </c>
+      <c r="K504" t="n">
+        <v>14</v>
+      </c>
+      <c r="L504" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>0</v>
+      </c>
+      <c r="D505" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="E505" t="n">
+        <v>0</v>
+      </c>
+      <c r="F505" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="G505" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H505" t="n">
+        <v>0</v>
+      </c>
+      <c r="I505" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="J505" t="n">
+        <v>0</v>
+      </c>
+      <c r="K505" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="L505" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>0</v>
+      </c>
+      <c r="D506" t="n">
+        <v>0</v>
+      </c>
+      <c r="E506" t="n">
+        <v>0</v>
+      </c>
+      <c r="F506" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G506" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H506" t="n">
+        <v>0</v>
+      </c>
+      <c r="I506" t="n">
+        <v>0</v>
+      </c>
+      <c r="J506" t="n">
+        <v>0</v>
+      </c>
+      <c r="K506" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="L506" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>0</v>
+      </c>
+      <c r="D507" t="n">
+        <v>0</v>
+      </c>
+      <c r="E507" t="n">
+        <v>0</v>
+      </c>
+      <c r="F507" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G507" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H507" t="n">
+        <v>0</v>
+      </c>
+      <c r="I507" t="n">
+        <v>0</v>
+      </c>
+      <c r="J507" t="n">
+        <v>0</v>
+      </c>
+      <c r="K507" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="L507" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>0</v>
+      </c>
+      <c r="D508" t="n">
+        <v>0</v>
+      </c>
+      <c r="E508" t="n">
+        <v>0</v>
+      </c>
+      <c r="F508" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G508" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H508" t="n">
+        <v>0</v>
+      </c>
+      <c r="I508" t="n">
+        <v>0</v>
+      </c>
+      <c r="J508" t="n">
+        <v>0</v>
+      </c>
+      <c r="K508" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="L508" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>0</v>
+      </c>
+      <c r="D509" t="n">
+        <v>0</v>
+      </c>
+      <c r="E509" t="n">
+        <v>0</v>
+      </c>
+      <c r="F509" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G509" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H509" t="n">
+        <v>0</v>
+      </c>
+      <c r="I509" t="n">
+        <v>0</v>
+      </c>
+      <c r="J509" t="n">
+        <v>0</v>
+      </c>
+      <c r="K509" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="L509" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>0</v>
+      </c>
+      <c r="D510" t="n">
+        <v>0</v>
+      </c>
+      <c r="E510" t="n">
+        <v>0</v>
+      </c>
+      <c r="F510" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G510" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H510" t="n">
+        <v>0</v>
+      </c>
+      <c r="I510" t="n">
+        <v>0</v>
+      </c>
+      <c r="J510" t="n">
+        <v>0</v>
+      </c>
+      <c r="K510" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L510" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>0</v>
+      </c>
+      <c r="D511" t="n">
+        <v>0</v>
+      </c>
+      <c r="E511" t="n">
+        <v>0</v>
+      </c>
+      <c r="F511" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G511" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H511" t="n">
+        <v>0</v>
+      </c>
+      <c r="I511" t="n">
+        <v>0</v>
+      </c>
+      <c r="J511" t="n">
+        <v>0</v>
+      </c>
+      <c r="K511" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L511" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>0</v>
+      </c>
+      <c r="D512" t="n">
+        <v>0</v>
+      </c>
+      <c r="E512" t="n">
+        <v>0</v>
+      </c>
+      <c r="F512" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G512" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H512" t="n">
+        <v>0</v>
+      </c>
+      <c r="I512" t="n">
+        <v>0</v>
+      </c>
+      <c r="J512" t="n">
+        <v>0</v>
+      </c>
+      <c r="K512" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L512" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="D513" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="E513" t="n">
+        <v>45</v>
+      </c>
+      <c r="F513" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G513" t="n">
         <v>2.7</v>
+      </c>
+      <c r="H513" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="I513" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="J513" t="n">
+        <v>45</v>
+      </c>
+      <c r="K513" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L513" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="D514" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="E514" t="n">
+        <v>146</v>
+      </c>
+      <c r="F514" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G514" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H514" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="I514" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="J514" t="n">
+        <v>146</v>
+      </c>
+      <c r="K514" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="L514" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="D515" t="n">
+        <v>42.12</v>
+      </c>
+      <c r="E515" t="n">
+        <v>326</v>
+      </c>
+      <c r="F515" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="G515" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H515" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="I515" t="n">
+        <v>42.12</v>
+      </c>
+      <c r="J515" t="n">
+        <v>326</v>
+      </c>
+      <c r="K515" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="L515" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="D516" t="n">
+        <v>87.09</v>
+      </c>
+      <c r="E516" t="n">
+        <v>576</v>
+      </c>
+      <c r="F516" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G516" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H516" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="I516" t="n">
+        <v>87.09</v>
+      </c>
+      <c r="J516" t="n">
+        <v>576</v>
+      </c>
+      <c r="K516" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L516" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="D517" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="E517" t="n">
+        <v>626</v>
+      </c>
+      <c r="F517" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G517" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H517" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="I517" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="J517" t="n">
+        <v>626</v>
+      </c>
+      <c r="K517" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="L517" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>56.91</v>
+      </c>
+      <c r="D518" t="n">
+        <v>192.33</v>
+      </c>
+      <c r="E518" t="n">
+        <v>754</v>
+      </c>
+      <c r="F518" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="G518" t="n">
+        <v>12</v>
+      </c>
+      <c r="H518" t="n">
+        <v>56.91</v>
+      </c>
+      <c r="I518" t="n">
+        <v>192.33</v>
+      </c>
+      <c r="J518" t="n">
+        <v>754</v>
+      </c>
+      <c r="K518" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="L518" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>55.36</v>
+      </c>
+      <c r="D519" t="n">
+        <v>247.69</v>
+      </c>
+      <c r="E519" t="n">
+        <v>732</v>
+      </c>
+      <c r="F519" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="G519" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H519" t="n">
+        <v>55.36</v>
+      </c>
+      <c r="I519" t="n">
+        <v>247.69</v>
+      </c>
+      <c r="J519" t="n">
+        <v>732</v>
+      </c>
+      <c r="K519" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="L519" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="D520" t="n">
+        <v>294.04</v>
+      </c>
+      <c r="E520" t="n">
+        <v>602</v>
+      </c>
+      <c r="F520" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="G520" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="H520" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="I520" t="n">
+        <v>294.04</v>
+      </c>
+      <c r="J520" t="n">
+        <v>602</v>
+      </c>
+      <c r="K520" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="L520" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>45.59</v>
+      </c>
+      <c r="D521" t="n">
+        <v>339.63</v>
+      </c>
+      <c r="E521" t="n">
+        <v>591</v>
+      </c>
+      <c r="F521" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="G521" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="H521" t="n">
+        <v>45.59</v>
+      </c>
+      <c r="I521" t="n">
+        <v>339.63</v>
+      </c>
+      <c r="J521" t="n">
+        <v>591</v>
+      </c>
+      <c r="K521" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="L521" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="D522" t="n">
+        <v>367.33</v>
+      </c>
+      <c r="E522" t="n">
+        <v>346</v>
+      </c>
+      <c r="F522" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G522" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H522" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="I522" t="n">
+        <v>367.33</v>
+      </c>
+      <c r="J522" t="n">
+        <v>346</v>
+      </c>
+      <c r="K522" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="L522" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="D523" t="n">
+        <v>392.54</v>
+      </c>
+      <c r="E523" t="n">
+        <v>312</v>
+      </c>
+      <c r="F523" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="G523" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H523" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="I523" t="n">
+        <v>392.54</v>
+      </c>
+      <c r="J523" t="n">
+        <v>312</v>
+      </c>
+      <c r="K523" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="L523" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="D524" t="n">
+        <v>407.15</v>
+      </c>
+      <c r="E524" t="n">
+        <v>179</v>
+      </c>
+      <c r="F524" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G524" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H524" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="I524" t="n">
+        <v>407.15</v>
+      </c>
+      <c r="J524" t="n">
+        <v>179</v>
+      </c>
+      <c r="K524" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="L524" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="D525" t="n">
+        <v>410.66</v>
+      </c>
+      <c r="E525" t="n">
+        <v>43</v>
+      </c>
+      <c r="F525" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G525" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="H525" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="I525" t="n">
+        <v>410.66</v>
+      </c>
+      <c r="J525" t="n">
+        <v>43</v>
+      </c>
+      <c r="K525" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L525" t="n">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>0</v>
+      </c>
+      <c r="D526" t="n">
+        <v>410.66</v>
+      </c>
+      <c r="E526" t="n">
+        <v>0</v>
+      </c>
+      <c r="F526" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G526" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H526" t="n">
+        <v>0</v>
+      </c>
+      <c r="I526" t="n">
+        <v>410.66</v>
+      </c>
+      <c r="J526" t="n">
+        <v>0</v>
+      </c>
+      <c r="K526" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L526" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>0</v>
+      </c>
+      <c r="D527" t="n">
+        <v>410.66</v>
+      </c>
+      <c r="E527" t="n">
+        <v>0</v>
+      </c>
+      <c r="F527" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G527" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H527" t="n">
+        <v>0</v>
+      </c>
+      <c r="I527" t="n">
+        <v>410.66</v>
+      </c>
+      <c r="J527" t="n">
+        <v>0</v>
+      </c>
+      <c r="K527" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L527" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>0</v>
+      </c>
+      <c r="D528" t="n">
+        <v>410.66</v>
+      </c>
+      <c r="E528" t="n">
+        <v>0</v>
+      </c>
+      <c r="F528" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G528" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H528" t="n">
+        <v>0</v>
+      </c>
+      <c r="I528" t="n">
+        <v>410.66</v>
+      </c>
+      <c r="J528" t="n">
+        <v>0</v>
+      </c>
+      <c r="K528" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L528" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>0</v>
+      </c>
+      <c r="D529" t="n">
+        <v>410.66</v>
+      </c>
+      <c r="E529" t="n">
+        <v>0</v>
+      </c>
+      <c r="F529" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G529" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H529" t="n">
+        <v>0</v>
+      </c>
+      <c r="I529" t="n">
+        <v>410.66</v>
+      </c>
+      <c r="J529" t="n">
+        <v>0</v>
+      </c>
+      <c r="K529" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L529" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>0</v>
+      </c>
+      <c r="D530" t="n">
+        <v>0</v>
+      </c>
+      <c r="E530" t="n">
+        <v>0</v>
+      </c>
+      <c r="F530" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G530" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H530" t="n">
+        <v>0</v>
+      </c>
+      <c r="I530" t="n">
+        <v>0</v>
+      </c>
+      <c r="J530" t="n">
+        <v>0</v>
+      </c>
+      <c r="K530" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L530" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>0</v>
+      </c>
+      <c r="D531" t="n">
+        <v>0</v>
+      </c>
+      <c r="E531" t="n">
+        <v>0</v>
+      </c>
+      <c r="F531" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G531" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H531" t="n">
+        <v>0</v>
+      </c>
+      <c r="I531" t="n">
+        <v>0</v>
+      </c>
+      <c r="J531" t="n">
+        <v>0</v>
+      </c>
+      <c r="K531" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L531" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>0</v>
+      </c>
+      <c r="D532" t="n">
+        <v>0</v>
+      </c>
+      <c r="E532" t="n">
+        <v>0</v>
+      </c>
+      <c r="F532" t="n">
+        <v>6</v>
+      </c>
+      <c r="G532" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H532" t="n">
+        <v>0</v>
+      </c>
+      <c r="I532" t="n">
+        <v>0</v>
+      </c>
+      <c r="J532" t="n">
+        <v>0</v>
+      </c>
+      <c r="K532" t="n">
+        <v>6</v>
+      </c>
+      <c r="L532" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>0</v>
+      </c>
+      <c r="D533" t="n">
+        <v>0</v>
+      </c>
+      <c r="E533" t="n">
+        <v>0</v>
+      </c>
+      <c r="F533" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G533" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H533" t="n">
+        <v>0</v>
+      </c>
+      <c r="I533" t="n">
+        <v>0</v>
+      </c>
+      <c r="J533" t="n">
+        <v>0</v>
+      </c>
+      <c r="K533" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L533" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>0</v>
+      </c>
+      <c r="D534" t="n">
+        <v>0</v>
+      </c>
+      <c r="E534" t="n">
+        <v>0</v>
+      </c>
+      <c r="F534" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G534" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H534" t="n">
+        <v>0</v>
+      </c>
+      <c r="I534" t="n">
+        <v>0</v>
+      </c>
+      <c r="J534" t="n">
+        <v>0</v>
+      </c>
+      <c r="K534" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L534" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>0</v>
+      </c>
+      <c r="D535" t="n">
+        <v>0</v>
+      </c>
+      <c r="E535" t="n">
+        <v>0</v>
+      </c>
+      <c r="F535" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G535" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H535" t="n">
+        <v>0</v>
+      </c>
+      <c r="I535" t="n">
+        <v>0</v>
+      </c>
+      <c r="J535" t="n">
+        <v>0</v>
+      </c>
+      <c r="K535" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="L535" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>0</v>
+      </c>
+      <c r="D536" t="n">
+        <v>0</v>
+      </c>
+      <c r="E536" t="n">
+        <v>0</v>
+      </c>
+      <c r="F536" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G536" t="n">
+        <v>18</v>
+      </c>
+      <c r="H536" t="n">
+        <v>0</v>
+      </c>
+      <c r="I536" t="n">
+        <v>0</v>
+      </c>
+      <c r="J536" t="n">
+        <v>0</v>
+      </c>
+      <c r="K536" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L536" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="D537" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="E537" t="n">
+        <v>66</v>
+      </c>
+      <c r="F537" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G537" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H537" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="I537" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="J537" t="n">
+        <v>66</v>
+      </c>
+      <c r="K537" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L537" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D538" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="E538" t="n">
+        <v>239</v>
+      </c>
+      <c r="F538" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G538" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H538" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I538" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="J538" t="n">
+        <v>239</v>
+      </c>
+      <c r="K538" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="L538" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="D539" t="n">
+        <v>62.51</v>
+      </c>
+      <c r="E539" t="n">
+        <v>462</v>
+      </c>
+      <c r="F539" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G539" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H539" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="I539" t="n">
+        <v>62.51</v>
+      </c>
+      <c r="J539" t="n">
+        <v>462</v>
+      </c>
+      <c r="K539" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L539" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="D540" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="E540" t="n">
+        <v>665</v>
+      </c>
+      <c r="F540" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G540" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H540" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="I540" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="J540" t="n">
+        <v>665</v>
+      </c>
+      <c r="K540" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="L540" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>62.29</v>
+      </c>
+      <c r="D541" t="n">
+        <v>177.09</v>
+      </c>
+      <c r="E541" t="n">
+        <v>812</v>
+      </c>
+      <c r="F541" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G541" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H541" t="n">
+        <v>62.29</v>
+      </c>
+      <c r="I541" t="n">
+        <v>177.09</v>
+      </c>
+      <c r="J541" t="n">
+        <v>812</v>
+      </c>
+      <c r="K541" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="L541" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>68.15000000000001</v>
+      </c>
+      <c r="D542" t="n">
+        <v>245.24</v>
+      </c>
+      <c r="E542" t="n">
+        <v>905</v>
+      </c>
+      <c r="F542" t="n">
+        <v>16</v>
+      </c>
+      <c r="G542" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H542" t="n">
+        <v>68.15000000000001</v>
+      </c>
+      <c r="I542" t="n">
+        <v>245.24</v>
+      </c>
+      <c r="J542" t="n">
+        <v>905</v>
+      </c>
+      <c r="K542" t="n">
+        <v>16</v>
+      </c>
+      <c r="L542" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>69.62</v>
+      </c>
+      <c r="D543" t="n">
+        <v>314.86</v>
+      </c>
+      <c r="E543" t="n">
+        <v>932</v>
+      </c>
+      <c r="F543" t="n">
+        <v>17</v>
+      </c>
+      <c r="G543" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H543" t="n">
+        <v>69.62</v>
+      </c>
+      <c r="I543" t="n">
+        <v>314.86</v>
+      </c>
+      <c r="J543" t="n">
+        <v>932</v>
+      </c>
+      <c r="K543" t="n">
+        <v>17</v>
+      </c>
+      <c r="L543" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="D544" t="n">
+        <v>381.46</v>
+      </c>
+      <c r="E544" t="n">
+        <v>889</v>
+      </c>
+      <c r="F544" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="G544" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H544" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="I544" t="n">
+        <v>381.46</v>
+      </c>
+      <c r="J544" t="n">
+        <v>889</v>
+      </c>
+      <c r="K544" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="L544" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="D545" t="n">
+        <v>441.15</v>
+      </c>
+      <c r="E545" t="n">
+        <v>785</v>
+      </c>
+      <c r="F545" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G545" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H545" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="I545" t="n">
+        <v>441.15</v>
+      </c>
+      <c r="J545" t="n">
+        <v>785</v>
+      </c>
+      <c r="K545" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="L545" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>49.24</v>
+      </c>
+      <c r="D546" t="n">
+        <v>490.39</v>
+      </c>
+      <c r="E546" t="n">
+        <v>633</v>
+      </c>
+      <c r="F546" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="G546" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H546" t="n">
+        <v>49.24</v>
+      </c>
+      <c r="I546" t="n">
+        <v>490.39</v>
+      </c>
+      <c r="J546" t="n">
+        <v>633</v>
+      </c>
+      <c r="K546" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="L546" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>35.09</v>
+      </c>
+      <c r="D547" t="n">
+        <v>525.48</v>
+      </c>
+      <c r="E547" t="n">
+        <v>437</v>
+      </c>
+      <c r="F547" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="G547" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H547" t="n">
+        <v>35.09</v>
+      </c>
+      <c r="I547" t="n">
+        <v>525.48</v>
+      </c>
+      <c r="J547" t="n">
+        <v>437</v>
+      </c>
+      <c r="K547" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="L547" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="D548" t="n">
+        <v>544</v>
+      </c>
+      <c r="E548" t="n">
+        <v>227</v>
+      </c>
+      <c r="F548" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G548" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H548" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="I548" t="n">
+        <v>544</v>
+      </c>
+      <c r="J548" t="n">
+        <v>227</v>
+      </c>
+      <c r="K548" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="L548" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="D549" t="n">
+        <v>548.49</v>
+      </c>
+      <c r="E549" t="n">
+        <v>55</v>
+      </c>
+      <c r="F549" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G549" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H549" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="I549" t="n">
+        <v>548.49</v>
+      </c>
+      <c r="J549" t="n">
+        <v>55</v>
+      </c>
+      <c r="K549" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L549" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>0</v>
+      </c>
+      <c r="D550" t="n">
+        <v>548.49</v>
+      </c>
+      <c r="E550" t="n">
+        <v>0</v>
+      </c>
+      <c r="F550" t="n">
+        <v>10</v>
+      </c>
+      <c r="G550" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H550" t="n">
+        <v>0</v>
+      </c>
+      <c r="I550" t="n">
+        <v>548.49</v>
+      </c>
+      <c r="J550" t="n">
+        <v>0</v>
+      </c>
+      <c r="K550" t="n">
+        <v>10</v>
+      </c>
+      <c r="L550" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>0</v>
+      </c>
+      <c r="D551" t="n">
+        <v>548.49</v>
+      </c>
+      <c r="E551" t="n">
+        <v>0</v>
+      </c>
+      <c r="F551" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G551" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H551" t="n">
+        <v>0</v>
+      </c>
+      <c r="I551" t="n">
+        <v>548.49</v>
+      </c>
+      <c r="J551" t="n">
+        <v>0</v>
+      </c>
+      <c r="K551" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="L551" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>0</v>
+      </c>
+      <c r="D552" t="n">
+        <v>548.49</v>
+      </c>
+      <c r="E552" t="n">
+        <v>0</v>
+      </c>
+      <c r="F552" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G552" t="n">
+        <v>6</v>
+      </c>
+      <c r="H552" t="n">
+        <v>0</v>
+      </c>
+      <c r="I552" t="n">
+        <v>548.49</v>
+      </c>
+      <c r="J552" t="n">
+        <v>0</v>
+      </c>
+      <c r="K552" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L552" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>0</v>
+      </c>
+      <c r="D553" t="n">
+        <v>548.49</v>
+      </c>
+      <c r="E553" t="n">
+        <v>0</v>
+      </c>
+      <c r="F553" t="n">
+        <v>11</v>
+      </c>
+      <c r="G553" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H553" t="n">
+        <v>0</v>
+      </c>
+      <c r="I553" t="n">
+        <v>548.49</v>
+      </c>
+      <c r="J553" t="n">
+        <v>0</v>
+      </c>
+      <c r="K553" t="n">
+        <v>11</v>
+      </c>
+      <c r="L553" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>0</v>
+      </c>
+      <c r="D554" t="n">
+        <v>0</v>
+      </c>
+      <c r="E554" t="n">
+        <v>0</v>
+      </c>
+      <c r="F554" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G554" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H554" t="n">
+        <v>0</v>
+      </c>
+      <c r="I554" t="n">
+        <v>0</v>
+      </c>
+      <c r="J554" t="n">
+        <v>0</v>
+      </c>
+      <c r="K554" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L554" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>0</v>
+      </c>
+      <c r="D555" t="n">
+        <v>0</v>
+      </c>
+      <c r="E555" t="n">
+        <v>0</v>
+      </c>
+      <c r="F555" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G555" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H555" t="n">
+        <v>0</v>
+      </c>
+      <c r="I555" t="n">
+        <v>0</v>
+      </c>
+      <c r="J555" t="n">
+        <v>0</v>
+      </c>
+      <c r="K555" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L555" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>0</v>
+      </c>
+      <c r="D556" t="n">
+        <v>0</v>
+      </c>
+      <c r="E556" t="n">
+        <v>0</v>
+      </c>
+      <c r="F556" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G556" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H556" t="n">
+        <v>0</v>
+      </c>
+      <c r="I556" t="n">
+        <v>0</v>
+      </c>
+      <c r="J556" t="n">
+        <v>0</v>
+      </c>
+      <c r="K556" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="L556" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>0</v>
+      </c>
+      <c r="D557" t="n">
+        <v>0</v>
+      </c>
+      <c r="E557" t="n">
+        <v>0</v>
+      </c>
+      <c r="F557" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G557" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H557" t="n">
+        <v>0</v>
+      </c>
+      <c r="I557" t="n">
+        <v>0</v>
+      </c>
+      <c r="J557" t="n">
+        <v>0</v>
+      </c>
+      <c r="K557" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L557" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>0</v>
+      </c>
+      <c r="D558" t="n">
+        <v>0</v>
+      </c>
+      <c r="E558" t="n">
+        <v>0</v>
+      </c>
+      <c r="F558" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G558" t="n">
+        <v>9</v>
+      </c>
+      <c r="H558" t="n">
+        <v>0</v>
+      </c>
+      <c r="I558" t="n">
+        <v>0</v>
+      </c>
+      <c r="J558" t="n">
+        <v>0</v>
+      </c>
+      <c r="K558" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="L558" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>0</v>
+      </c>
+      <c r="D559" t="n">
+        <v>0</v>
+      </c>
+      <c r="E559" t="n">
+        <v>0</v>
+      </c>
+      <c r="F559" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G559" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H559" t="n">
+        <v>0</v>
+      </c>
+      <c r="I559" t="n">
+        <v>0</v>
+      </c>
+      <c r="J559" t="n">
+        <v>0</v>
+      </c>
+      <c r="K559" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="L559" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>0</v>
+      </c>
+      <c r="D560" t="n">
+        <v>0</v>
+      </c>
+      <c r="E560" t="n">
+        <v>0</v>
+      </c>
+      <c r="F560" t="n">
+        <v>10</v>
+      </c>
+      <c r="G560" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H560" t="n">
+        <v>0</v>
+      </c>
+      <c r="I560" t="n">
+        <v>0</v>
+      </c>
+      <c r="J560" t="n">
+        <v>0</v>
+      </c>
+      <c r="K560" t="n">
+        <v>10</v>
+      </c>
+      <c r="L560" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D561" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E561" t="n">
+        <v>15</v>
+      </c>
+      <c r="F561" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G561" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H561" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I561" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J561" t="n">
+        <v>15</v>
+      </c>
+      <c r="K561" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="L561" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>4</v>
+      </c>
+      <c r="D562" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="E562" t="n">
+        <v>49</v>
+      </c>
+      <c r="F562" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G562" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H562" t="n">
+        <v>4</v>
+      </c>
+      <c r="I562" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="J562" t="n">
+        <v>49</v>
+      </c>
+      <c r="K562" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L562" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="D563" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="E563" t="n">
+        <v>95</v>
+      </c>
+      <c r="F563" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G563" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H563" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="I563" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="J563" t="n">
+        <v>95</v>
+      </c>
+      <c r="K563" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="L563" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="D564" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="E564" t="n">
+        <v>155</v>
+      </c>
+      <c r="F564" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G564" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H564" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="I564" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="J564" t="n">
+        <v>155</v>
+      </c>
+      <c r="K564" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="L564" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="D565" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="E565" t="n">
+        <v>126</v>
+      </c>
+      <c r="F565" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G565" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H565" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="I565" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="J565" t="n">
+        <v>126</v>
+      </c>
+      <c r="K565" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L565" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="D566" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="E566" t="n">
+        <v>160</v>
+      </c>
+      <c r="F566" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G566" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H566" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="I566" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="J566" t="n">
+        <v>160</v>
+      </c>
+      <c r="K566" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="L566" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="D567" t="n">
+        <v>63.48</v>
+      </c>
+      <c r="E567" t="n">
+        <v>178</v>
+      </c>
+      <c r="F567" t="n">
+        <v>13</v>
+      </c>
+      <c r="G567" t="n">
+        <v>12</v>
+      </c>
+      <c r="H567" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="I567" t="n">
+        <v>63.48</v>
+      </c>
+      <c r="J567" t="n">
+        <v>178</v>
+      </c>
+      <c r="K567" t="n">
+        <v>13</v>
+      </c>
+      <c r="L567" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="D568" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="E568" t="n">
+        <v>211</v>
+      </c>
+      <c r="F568" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G568" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H568" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="I568" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="J568" t="n">
+        <v>211</v>
+      </c>
+      <c r="K568" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="L568" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D569" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="E569" t="n">
+        <v>136</v>
+      </c>
+      <c r="F569" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G569" t="n">
+        <v>16</v>
+      </c>
+      <c r="H569" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I569" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="J569" t="n">
+        <v>136</v>
+      </c>
+      <c r="K569" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L569" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="D570" t="n">
+        <v>100.69</v>
+      </c>
+      <c r="E570" t="n">
+        <v>109</v>
+      </c>
+      <c r="F570" t="n">
+        <v>12</v>
+      </c>
+      <c r="G570" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H570" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="I570" t="n">
+        <v>100.69</v>
+      </c>
+      <c r="J570" t="n">
+        <v>109</v>
+      </c>
+      <c r="K570" t="n">
+        <v>12</v>
+      </c>
+      <c r="L570" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="D571" t="n">
+        <v>104.36</v>
+      </c>
+      <c r="E571" t="n">
+        <v>45</v>
+      </c>
+      <c r="F571" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G571" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H571" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="I571" t="n">
+        <v>104.36</v>
+      </c>
+      <c r="J571" t="n">
+        <v>45</v>
+      </c>
+      <c r="K571" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L571" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="D572" t="n">
+        <v>106.73</v>
+      </c>
+      <c r="E572" t="n">
+        <v>29</v>
+      </c>
+      <c r="F572" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G572" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H572" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="I572" t="n">
+        <v>106.73</v>
+      </c>
+      <c r="J572" t="n">
+        <v>29</v>
+      </c>
+      <c r="K572" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L572" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D573" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="E573" t="n">
+        <v>8</v>
+      </c>
+      <c r="F573" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G573" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H573" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I573" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="J573" t="n">
+        <v>8</v>
+      </c>
+      <c r="K573" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L573" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>0</v>
+      </c>
+      <c r="D574" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="E574" t="n">
+        <v>0</v>
+      </c>
+      <c r="F574" t="n">
+        <v>9</v>
+      </c>
+      <c r="G574" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H574" t="n">
+        <v>0</v>
+      </c>
+      <c r="I574" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="J574" t="n">
+        <v>0</v>
+      </c>
+      <c r="K574" t="n">
+        <v>9</v>
+      </c>
+      <c r="L574" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>0</v>
+      </c>
+      <c r="D575" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="E575" t="n">
+        <v>0</v>
+      </c>
+      <c r="F575" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G575" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H575" t="n">
+        <v>0</v>
+      </c>
+      <c r="I575" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="J575" t="n">
+        <v>0</v>
+      </c>
+      <c r="K575" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="L575" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>0</v>
+      </c>
+      <c r="D576" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="E576" t="n">
+        <v>0</v>
+      </c>
+      <c r="F576" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G576" t="n">
+        <v>8</v>
+      </c>
+      <c r="H576" t="n">
+        <v>0</v>
+      </c>
+      <c r="I576" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="J576" t="n">
+        <v>0</v>
+      </c>
+      <c r="K576" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L576" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>0</v>
+      </c>
+      <c r="D577" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="E577" t="n">
+        <v>0</v>
+      </c>
+      <c r="F577" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G577" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H577" t="n">
+        <v>0</v>
+      </c>
+      <c r="I577" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="J577" t="n">
+        <v>0</v>
+      </c>
+      <c r="K577" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L577" t="n">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1921"/>
+  <dimension ref="A1:L1945"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81598,6 +81598,1014 @@
         <v>10.7</v>
       </c>
     </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C1922" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1922" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1922" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1922" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G1922" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H1922" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1922" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1922" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1922" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="L1922" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C1923" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1923" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1923" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1923" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G1923" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H1923" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1923" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1923" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1923" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="L1923" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C1924" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1924" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1924" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1924" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G1924" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H1924" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1924" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1924" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1924" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="L1924" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C1925" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1925" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1925" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1925" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G1925" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H1925" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1925" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1925" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1925" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="L1925" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C1926" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1926" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1926" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1926" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G1926" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H1926" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1926" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1926" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1926" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="L1926" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C1927" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1927" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1927" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1927" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G1927" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H1927" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1927" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1927" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1927" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="L1927" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C1928" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D1928" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E1928" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1928" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G1928" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H1928" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I1928" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J1928" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1928" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="L1928" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C1929" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="D1929" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="E1929" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1929" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G1929" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H1929" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="I1929" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="J1929" t="n">
+        <v>40</v>
+      </c>
+      <c r="K1929" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="L1929" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C1930" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="D1930" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="E1930" t="n">
+        <v>91</v>
+      </c>
+      <c r="F1930" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G1930" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H1930" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="I1930" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="J1930" t="n">
+        <v>91</v>
+      </c>
+      <c r="K1930" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="L1930" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C1931" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="D1931" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="E1931" t="n">
+        <v>220</v>
+      </c>
+      <c r="F1931" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G1931" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1931" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="I1931" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="J1931" t="n">
+        <v>220</v>
+      </c>
+      <c r="K1931" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="L1931" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C1932" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="D1932" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="E1932" t="n">
+        <v>258</v>
+      </c>
+      <c r="F1932" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G1932" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H1932" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="I1932" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="J1932" t="n">
+        <v>258</v>
+      </c>
+      <c r="K1932" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="L1932" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C1933" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="D1933" t="n">
+        <v>73.45</v>
+      </c>
+      <c r="E1933" t="n">
+        <v>315</v>
+      </c>
+      <c r="F1933" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G1933" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H1933" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="I1933" t="n">
+        <v>73.45</v>
+      </c>
+      <c r="J1933" t="n">
+        <v>315</v>
+      </c>
+      <c r="K1933" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="L1933" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C1934" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="D1934" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="E1934" t="n">
+        <v>498</v>
+      </c>
+      <c r="F1934" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G1934" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H1934" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="I1934" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="J1934" t="n">
+        <v>498</v>
+      </c>
+      <c r="K1934" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="L1934" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C1935" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="D1935" t="n">
+        <v>163.58</v>
+      </c>
+      <c r="E1935" t="n">
+        <v>716</v>
+      </c>
+      <c r="F1935" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G1935" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H1935" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="I1935" t="n">
+        <v>163.58</v>
+      </c>
+      <c r="J1935" t="n">
+        <v>716</v>
+      </c>
+      <c r="K1935" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L1935" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C1936" t="n">
+        <v>47.77</v>
+      </c>
+      <c r="D1936" t="n">
+        <v>211.35</v>
+      </c>
+      <c r="E1936" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1936" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G1936" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1936" t="n">
+        <v>47.77</v>
+      </c>
+      <c r="I1936" t="n">
+        <v>211.35</v>
+      </c>
+      <c r="J1936" t="n">
+        <v>649</v>
+      </c>
+      <c r="K1936" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="L1936" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C1937" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="D1937" t="n">
+        <v>260.72</v>
+      </c>
+      <c r="E1937" t="n">
+        <v>672</v>
+      </c>
+      <c r="F1937" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G1937" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H1937" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="I1937" t="n">
+        <v>260.72</v>
+      </c>
+      <c r="J1937" t="n">
+        <v>672</v>
+      </c>
+      <c r="K1937" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="L1937" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C1938" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="D1938" t="n">
+        <v>298.77</v>
+      </c>
+      <c r="E1938" t="n">
+        <v>507</v>
+      </c>
+      <c r="F1938" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G1938" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H1938" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="I1938" t="n">
+        <v>298.77</v>
+      </c>
+      <c r="J1938" t="n">
+        <v>507</v>
+      </c>
+      <c r="K1938" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="L1938" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C1939" t="n">
+        <v>29.67</v>
+      </c>
+      <c r="D1939" t="n">
+        <v>328.44</v>
+      </c>
+      <c r="E1939" t="n">
+        <v>389</v>
+      </c>
+      <c r="F1939" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G1939" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H1939" t="n">
+        <v>29.67</v>
+      </c>
+      <c r="I1939" t="n">
+        <v>328.44</v>
+      </c>
+      <c r="J1939" t="n">
+        <v>389</v>
+      </c>
+      <c r="K1939" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="L1939" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C1940" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D1940" t="n">
+        <v>349.04</v>
+      </c>
+      <c r="E1940" t="n">
+        <v>265</v>
+      </c>
+      <c r="F1940" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G1940" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H1940" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="I1940" t="n">
+        <v>349.04</v>
+      </c>
+      <c r="J1940" t="n">
+        <v>265</v>
+      </c>
+      <c r="K1940" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="L1940" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C1941" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="D1941" t="n">
+        <v>357.26</v>
+      </c>
+      <c r="E1941" t="n">
+        <v>103</v>
+      </c>
+      <c r="F1941" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="G1941" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H1941" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="I1941" t="n">
+        <v>357.26</v>
+      </c>
+      <c r="J1941" t="n">
+        <v>103</v>
+      </c>
+      <c r="K1941" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="L1941" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C1942" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D1942" t="n">
+        <v>358.31</v>
+      </c>
+      <c r="E1942" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1942" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G1942" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H1942" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I1942" t="n">
+        <v>358.31</v>
+      </c>
+      <c r="J1942" t="n">
+        <v>13</v>
+      </c>
+      <c r="K1942" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="L1942" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C1943" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1943" t="n">
+        <v>358.31</v>
+      </c>
+      <c r="E1943" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1943" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="G1943" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H1943" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1943" t="n">
+        <v>358.31</v>
+      </c>
+      <c r="J1943" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1943" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="L1943" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1944" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C1944" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1944" t="n">
+        <v>358.31</v>
+      </c>
+      <c r="E1944" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1944" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G1944" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H1944" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1944" t="n">
+        <v>358.31</v>
+      </c>
+      <c r="J1944" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1944" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="L1944" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C1945" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1945" t="n">
+        <v>358.31</v>
+      </c>
+      <c r="E1945" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1945" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G1945" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H1945" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1945" t="n">
+        <v>358.31</v>
+      </c>
+      <c r="J1945" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1945" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="L1945" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/log.xlsx
+++ b/log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1945"/>
+  <dimension ref="A1:L1969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82606,6 +82606,1014 @@
         <v>7.2</v>
       </c>
     </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C1946" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1946" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1946" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1946" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G1946" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H1946" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1946" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1946" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1946" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="L1946" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C1947" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1947" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1947" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1947" t="n">
+        <v>23</v>
+      </c>
+      <c r="G1947" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1947" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1947" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1947" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1947" t="n">
+        <v>23</v>
+      </c>
+      <c r="L1947" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C1948" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1948" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1948" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1948" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G1948" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1948" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1948" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1948" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1948" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="L1948" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C1949" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1949" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1949" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1949" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G1949" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1949" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1949" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1949" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1949" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="L1949" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C1950" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1950" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1950" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1950" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G1950" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H1950" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1950" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1950" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1950" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="L1950" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C1951" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1951" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1951" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1951" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G1951" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H1951" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1951" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1951" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1951" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="L1951" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C1952" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="D1952" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E1952" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1952" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G1952" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H1952" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I1952" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J1952" t="n">
+        <v>7</v>
+      </c>
+      <c r="K1952" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="L1952" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C1953" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="D1953" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="E1953" t="n">
+        <v>84</v>
+      </c>
+      <c r="F1953" t="n">
+        <v>23</v>
+      </c>
+      <c r="G1953" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H1953" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="I1953" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="J1953" t="n">
+        <v>84</v>
+      </c>
+      <c r="K1953" t="n">
+        <v>23</v>
+      </c>
+      <c r="L1953" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C1954" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="D1954" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="E1954" t="n">
+        <v>145</v>
+      </c>
+      <c r="F1954" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G1954" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H1954" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="I1954" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="J1954" t="n">
+        <v>145</v>
+      </c>
+      <c r="K1954" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="L1954" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C1955" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="D1955" t="n">
+        <v>48.91</v>
+      </c>
+      <c r="E1955" t="n">
+        <v>385</v>
+      </c>
+      <c r="F1955" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G1955" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H1955" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="I1955" t="n">
+        <v>48.91</v>
+      </c>
+      <c r="J1955" t="n">
+        <v>385</v>
+      </c>
+      <c r="K1955" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="L1955" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C1956" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="D1956" t="n">
+        <v>93.02</v>
+      </c>
+      <c r="E1956" t="n">
+        <v>588</v>
+      </c>
+      <c r="F1956" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G1956" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H1956" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="I1956" t="n">
+        <v>93.02</v>
+      </c>
+      <c r="J1956" t="n">
+        <v>588</v>
+      </c>
+      <c r="K1956" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="L1956" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C1957" t="n">
+        <v>57.17</v>
+      </c>
+      <c r="D1957" t="n">
+        <v>150.19</v>
+      </c>
+      <c r="E1957" t="n">
+        <v>790</v>
+      </c>
+      <c r="F1957" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G1957" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H1957" t="n">
+        <v>57.17</v>
+      </c>
+      <c r="I1957" t="n">
+        <v>150.19</v>
+      </c>
+      <c r="J1957" t="n">
+        <v>790</v>
+      </c>
+      <c r="K1957" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="L1957" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C1958" t="n">
+        <v>60.53</v>
+      </c>
+      <c r="D1958" t="n">
+        <v>210.72</v>
+      </c>
+      <c r="E1958" t="n">
+        <v>847</v>
+      </c>
+      <c r="F1958" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="G1958" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H1958" t="n">
+        <v>60.53</v>
+      </c>
+      <c r="I1958" t="n">
+        <v>210.72</v>
+      </c>
+      <c r="J1958" t="n">
+        <v>847</v>
+      </c>
+      <c r="K1958" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="L1958" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C1959" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="D1959" t="n">
+        <v>272.57</v>
+      </c>
+      <c r="E1959" t="n">
+        <v>869</v>
+      </c>
+      <c r="F1959" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="G1959" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H1959" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="I1959" t="n">
+        <v>272.57</v>
+      </c>
+      <c r="J1959" t="n">
+        <v>869</v>
+      </c>
+      <c r="K1959" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="L1959" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C1960" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="D1960" t="n">
+        <v>334.42</v>
+      </c>
+      <c r="E1960" t="n">
+        <v>870</v>
+      </c>
+      <c r="F1960" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1960" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H1960" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="I1960" t="n">
+        <v>334.42</v>
+      </c>
+      <c r="J1960" t="n">
+        <v>870</v>
+      </c>
+      <c r="K1960" t="n">
+        <v>30</v>
+      </c>
+      <c r="L1960" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C1961" t="n">
+        <v>53.91</v>
+      </c>
+      <c r="D1961" t="n">
+        <v>388.33</v>
+      </c>
+      <c r="E1961" t="n">
+        <v>745</v>
+      </c>
+      <c r="F1961" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1961" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H1961" t="n">
+        <v>53.91</v>
+      </c>
+      <c r="I1961" t="n">
+        <v>388.33</v>
+      </c>
+      <c r="J1961" t="n">
+        <v>745</v>
+      </c>
+      <c r="K1961" t="n">
+        <v>30</v>
+      </c>
+      <c r="L1961" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C1962" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="D1962" t="n">
+        <v>436.28</v>
+      </c>
+      <c r="E1962" t="n">
+        <v>652</v>
+      </c>
+      <c r="F1962" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="G1962" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1962" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="I1962" t="n">
+        <v>436.28</v>
+      </c>
+      <c r="J1962" t="n">
+        <v>652</v>
+      </c>
+      <c r="K1962" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="L1962" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C1963" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="D1963" t="n">
+        <v>473.22</v>
+      </c>
+      <c r="E1963" t="n">
+        <v>490</v>
+      </c>
+      <c r="F1963" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G1963" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H1963" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="I1963" t="n">
+        <v>473.22</v>
+      </c>
+      <c r="J1963" t="n">
+        <v>490</v>
+      </c>
+      <c r="K1963" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L1963" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C1964" t="n">
+        <v>24.09</v>
+      </c>
+      <c r="D1964" t="n">
+        <v>497.31</v>
+      </c>
+      <c r="E1964" t="n">
+        <v>311</v>
+      </c>
+      <c r="F1964" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1964" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="H1964" t="n">
+        <v>24.09</v>
+      </c>
+      <c r="I1964" t="n">
+        <v>497.31</v>
+      </c>
+      <c r="J1964" t="n">
+        <v>311</v>
+      </c>
+      <c r="K1964" t="n">
+        <v>28</v>
+      </c>
+      <c r="L1964" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C1965" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="D1965" t="n">
+        <v>508.04</v>
+      </c>
+      <c r="E1965" t="n">
+        <v>135</v>
+      </c>
+      <c r="F1965" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="G1965" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1965" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="I1965" t="n">
+        <v>508.04</v>
+      </c>
+      <c r="J1965" t="n">
+        <v>135</v>
+      </c>
+      <c r="K1965" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="L1965" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C1966" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D1966" t="n">
+        <v>509.26</v>
+      </c>
+      <c r="E1966" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1966" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1966" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H1966" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I1966" t="n">
+        <v>509.26</v>
+      </c>
+      <c r="J1966" t="n">
+        <v>15</v>
+      </c>
+      <c r="K1966" t="n">
+        <v>26</v>
+      </c>
+      <c r="L1966" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C1967" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1967" t="n">
+        <v>509.26</v>
+      </c>
+      <c r="E1967" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1967" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G1967" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H1967" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1967" t="n">
+        <v>509.26</v>
+      </c>
+      <c r="J1967" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1967" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="L1967" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1968" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C1968" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1968" t="n">
+        <v>509.26</v>
+      </c>
+      <c r="E1968" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1968" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1968" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H1968" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1968" t="n">
+        <v>509.26</v>
+      </c>
+      <c r="J1968" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1968" t="n">
+        <v>25</v>
+      </c>
+      <c r="L1968" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C1969" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1969" t="n">
+        <v>509.26</v>
+      </c>
+      <c r="E1969" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1969" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G1969" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H1969" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1969" t="n">
+        <v>509.26</v>
+      </c>
+      <c r="J1969" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1969" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="L1969" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/log.xlsx
+++ b/log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1969"/>
+  <dimension ref="A1:L1993"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83614,6 +83614,1014 @@
         <v>7.2</v>
       </c>
     </row>
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C1970" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1970" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1970" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1970" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G1970" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1970" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1970" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1970" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1970" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="L1970" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C1971" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1971" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1971" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1971" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G1971" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H1971" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1971" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1971" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1971" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="L1971" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C1972" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1972" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1972" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1972" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1972" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H1972" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1972" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1972" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1972" t="n">
+        <v>25</v>
+      </c>
+      <c r="L1972" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C1973" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1973" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1973" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1973" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G1973" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H1973" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1973" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1973" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1973" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="L1973" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C1974" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1974" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1974" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1974" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G1974" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H1974" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1974" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1974" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1974" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="L1974" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C1975" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1975" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1975" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1975" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G1975" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H1975" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1975" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1975" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1975" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="L1975" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C1976" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="D1976" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E1976" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1976" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G1976" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H1976" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I1976" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J1976" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1976" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="L1976" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C1977" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="D1977" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="E1977" t="n">
+        <v>108</v>
+      </c>
+      <c r="F1977" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G1977" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H1977" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="I1977" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="J1977" t="n">
+        <v>108</v>
+      </c>
+      <c r="K1977" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="L1977" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C1978" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="D1978" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="E1978" t="n">
+        <v>297</v>
+      </c>
+      <c r="F1978" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G1978" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H1978" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="I1978" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="J1978" t="n">
+        <v>297</v>
+      </c>
+      <c r="K1978" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="L1978" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C1979" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="D1979" t="n">
+        <v>69.41</v>
+      </c>
+      <c r="E1979" t="n">
+        <v>492</v>
+      </c>
+      <c r="F1979" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G1979" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H1979" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="I1979" t="n">
+        <v>69.41</v>
+      </c>
+      <c r="J1979" t="n">
+        <v>492</v>
+      </c>
+      <c r="K1979" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L1979" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C1980" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="D1980" t="n">
+        <v>118.72</v>
+      </c>
+      <c r="E1980" t="n">
+        <v>675</v>
+      </c>
+      <c r="F1980" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="G1980" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H1980" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="I1980" t="n">
+        <v>118.72</v>
+      </c>
+      <c r="J1980" t="n">
+        <v>675</v>
+      </c>
+      <c r="K1980" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="L1980" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C1981" t="n">
+        <v>58.21</v>
+      </c>
+      <c r="D1981" t="n">
+        <v>176.93</v>
+      </c>
+      <c r="E1981" t="n">
+        <v>820</v>
+      </c>
+      <c r="F1981" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="G1981" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H1981" t="n">
+        <v>58.21</v>
+      </c>
+      <c r="I1981" t="n">
+        <v>176.93</v>
+      </c>
+      <c r="J1981" t="n">
+        <v>820</v>
+      </c>
+      <c r="K1981" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="L1981" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C1982" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="D1982" t="n">
+        <v>240.43</v>
+      </c>
+      <c r="E1982" t="n">
+        <v>913</v>
+      </c>
+      <c r="F1982" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="G1982" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H1982" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="I1982" t="n">
+        <v>240.43</v>
+      </c>
+      <c r="J1982" t="n">
+        <v>913</v>
+      </c>
+      <c r="K1982" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="L1982" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C1983" t="n">
+        <v>65.19</v>
+      </c>
+      <c r="D1983" t="n">
+        <v>305.62</v>
+      </c>
+      <c r="E1983" t="n">
+        <v>947</v>
+      </c>
+      <c r="F1983" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="G1983" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H1983" t="n">
+        <v>65.19</v>
+      </c>
+      <c r="I1983" t="n">
+        <v>305.62</v>
+      </c>
+      <c r="J1983" t="n">
+        <v>947</v>
+      </c>
+      <c r="K1983" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="L1983" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C1984" t="n">
+        <v>63.29</v>
+      </c>
+      <c r="D1984" t="n">
+        <v>368.91</v>
+      </c>
+      <c r="E1984" t="n">
+        <v>919</v>
+      </c>
+      <c r="F1984" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="G1984" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H1984" t="n">
+        <v>63.29</v>
+      </c>
+      <c r="I1984" t="n">
+        <v>368.91</v>
+      </c>
+      <c r="J1984" t="n">
+        <v>919</v>
+      </c>
+      <c r="K1984" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="L1984" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C1985" t="n">
+        <v>57.84</v>
+      </c>
+      <c r="D1985" t="n">
+        <v>426.75</v>
+      </c>
+      <c r="E1985" t="n">
+        <v>832</v>
+      </c>
+      <c r="F1985" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1985" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H1985" t="n">
+        <v>57.84</v>
+      </c>
+      <c r="I1985" t="n">
+        <v>426.75</v>
+      </c>
+      <c r="J1985" t="n">
+        <v>832</v>
+      </c>
+      <c r="K1985" t="n">
+        <v>36</v>
+      </c>
+      <c r="L1985" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C1986" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="D1986" t="n">
+        <v>476.18</v>
+      </c>
+      <c r="E1986" t="n">
+        <v>694</v>
+      </c>
+      <c r="F1986" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="G1986" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H1986" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="I1986" t="n">
+        <v>476.18</v>
+      </c>
+      <c r="J1986" t="n">
+        <v>694</v>
+      </c>
+      <c r="K1986" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L1986" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C1987" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="D1987" t="n">
+        <v>513.97</v>
+      </c>
+      <c r="E1987" t="n">
+        <v>515</v>
+      </c>
+      <c r="F1987" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="G1987" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H1987" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="I1987" t="n">
+        <v>513.97</v>
+      </c>
+      <c r="J1987" t="n">
+        <v>515</v>
+      </c>
+      <c r="K1987" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="L1987" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C1988" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="D1988" t="n">
+        <v>537.98</v>
+      </c>
+      <c r="E1988" t="n">
+        <v>317</v>
+      </c>
+      <c r="F1988" t="n">
+        <v>33</v>
+      </c>
+      <c r="G1988" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H1988" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="I1988" t="n">
+        <v>537.98</v>
+      </c>
+      <c r="J1988" t="n">
+        <v>317</v>
+      </c>
+      <c r="K1988" t="n">
+        <v>33</v>
+      </c>
+      <c r="L1988" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C1989" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D1989" t="n">
+        <v>548.28</v>
+      </c>
+      <c r="E1989" t="n">
+        <v>132</v>
+      </c>
+      <c r="F1989" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="G1989" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H1989" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I1989" t="n">
+        <v>548.28</v>
+      </c>
+      <c r="J1989" t="n">
+        <v>132</v>
+      </c>
+      <c r="K1989" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="L1989" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C1990" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D1990" t="n">
+        <v>549.08</v>
+      </c>
+      <c r="E1990" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1990" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1990" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H1990" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I1990" t="n">
+        <v>549.08</v>
+      </c>
+      <c r="J1990" t="n">
+        <v>10</v>
+      </c>
+      <c r="K1990" t="n">
+        <v>30</v>
+      </c>
+      <c r="L1990" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C1991" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1991" t="n">
+        <v>549.08</v>
+      </c>
+      <c r="E1991" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1991" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="G1991" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H1991" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1991" t="n">
+        <v>549.08</v>
+      </c>
+      <c r="J1991" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1991" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="L1991" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C1992" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1992" t="n">
+        <v>549.08</v>
+      </c>
+      <c r="E1992" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1992" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="G1992" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H1992" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1992" t="n">
+        <v>549.08</v>
+      </c>
+      <c r="J1992" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1992" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="L1992" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C1993" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1993" t="n">
+        <v>549.08</v>
+      </c>
+      <c r="E1993" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1993" t="n">
+        <v>27</v>
+      </c>
+      <c r="G1993" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H1993" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1993" t="n">
+        <v>549.08</v>
+      </c>
+      <c r="J1993" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1993" t="n">
+        <v>27</v>
+      </c>
+      <c r="L1993" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/log.xlsx
+++ b/log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1993"/>
+  <dimension ref="A1:L2017"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84622,6 +84622,1014 @@
         <v>4.4</v>
       </c>
     </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C1994" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1994" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1994" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1994" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1994" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H1994" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1994" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1994" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1994" t="n">
+        <v>26</v>
+      </c>
+      <c r="L1994" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C1995" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1995" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1995" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1995" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="G1995" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H1995" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1995" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1995" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1995" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="L1995" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1996" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G1996" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1996" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="L1996" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1997" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G1997" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1997" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="L1997" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1998" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G1998" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1998" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="L1998" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1999" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G1999" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1999" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="L1999" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C2000" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D2000" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E2000" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2000" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G2000" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H2000" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I2000" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J2000" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2000" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="L2000" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C2001" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="D2001" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E2001" t="n">
+        <v>105</v>
+      </c>
+      <c r="F2001" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G2001" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2001" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="I2001" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J2001" t="n">
+        <v>105</v>
+      </c>
+      <c r="K2001" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="L2001" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C2002" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="D2002" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="E2002" t="n">
+        <v>294</v>
+      </c>
+      <c r="F2002" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G2002" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H2002" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="I2002" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="J2002" t="n">
+        <v>294</v>
+      </c>
+      <c r="K2002" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="L2002" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C2003" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="D2003" t="n">
+        <v>69.03</v>
+      </c>
+      <c r="E2003" t="n">
+        <v>496</v>
+      </c>
+      <c r="F2003" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="G2003" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2003" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="I2003" t="n">
+        <v>69.03</v>
+      </c>
+      <c r="J2003" t="n">
+        <v>496</v>
+      </c>
+      <c r="K2003" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="L2003" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C2004" t="n">
+        <v>49.07</v>
+      </c>
+      <c r="D2004" t="n">
+        <v>118.1</v>
+      </c>
+      <c r="E2004" t="n">
+        <v>675</v>
+      </c>
+      <c r="F2004" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="G2004" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H2004" t="n">
+        <v>49.07</v>
+      </c>
+      <c r="I2004" t="n">
+        <v>118.1</v>
+      </c>
+      <c r="J2004" t="n">
+        <v>675</v>
+      </c>
+      <c r="K2004" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="L2004" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C2005" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="D2005" t="n">
+        <v>175.59</v>
+      </c>
+      <c r="E2005" t="n">
+        <v>815</v>
+      </c>
+      <c r="F2005" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="G2005" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H2005" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="I2005" t="n">
+        <v>175.59</v>
+      </c>
+      <c r="J2005" t="n">
+        <v>815</v>
+      </c>
+      <c r="K2005" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="L2005" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C2006" t="n">
+        <v>62.63</v>
+      </c>
+      <c r="D2006" t="n">
+        <v>238.22</v>
+      </c>
+      <c r="E2006" t="n">
+        <v>906</v>
+      </c>
+      <c r="F2006" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="G2006" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H2006" t="n">
+        <v>62.63</v>
+      </c>
+      <c r="I2006" t="n">
+        <v>238.22</v>
+      </c>
+      <c r="J2006" t="n">
+        <v>906</v>
+      </c>
+      <c r="K2006" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="L2006" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C2007" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="D2007" t="n">
+        <v>302.45</v>
+      </c>
+      <c r="E2007" t="n">
+        <v>938</v>
+      </c>
+      <c r="F2007" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="G2007" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2007" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="I2007" t="n">
+        <v>302.45</v>
+      </c>
+      <c r="J2007" t="n">
+        <v>938</v>
+      </c>
+      <c r="K2007" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="L2007" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C2008" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="D2008" t="n">
+        <v>364.72</v>
+      </c>
+      <c r="E2008" t="n">
+        <v>910</v>
+      </c>
+      <c r="F2008" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="G2008" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H2008" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="I2008" t="n">
+        <v>364.72</v>
+      </c>
+      <c r="J2008" t="n">
+        <v>910</v>
+      </c>
+      <c r="K2008" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="L2008" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C2009" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="D2009" t="n">
+        <v>421.23</v>
+      </c>
+      <c r="E2009" t="n">
+        <v>819</v>
+      </c>
+      <c r="F2009" t="n">
+        <v>38</v>
+      </c>
+      <c r="G2009" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H2009" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="I2009" t="n">
+        <v>421.23</v>
+      </c>
+      <c r="J2009" t="n">
+        <v>819</v>
+      </c>
+      <c r="K2009" t="n">
+        <v>38</v>
+      </c>
+      <c r="L2009" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C2010" t="n">
+        <v>46.91</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>468.14</v>
+      </c>
+      <c r="E2010" t="n">
+        <v>663</v>
+      </c>
+      <c r="F2010" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G2010" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H2010" t="n">
+        <v>46.91</v>
+      </c>
+      <c r="I2010" t="n">
+        <v>468.14</v>
+      </c>
+      <c r="J2010" t="n">
+        <v>663</v>
+      </c>
+      <c r="K2010" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L2010" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C2011" t="n">
+        <v>36.22</v>
+      </c>
+      <c r="D2011" t="n">
+        <v>504.36</v>
+      </c>
+      <c r="E2011" t="n">
+        <v>499</v>
+      </c>
+      <c r="F2011" t="n">
+        <v>37</v>
+      </c>
+      <c r="G2011" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H2011" t="n">
+        <v>36.22</v>
+      </c>
+      <c r="I2011" t="n">
+        <v>504.36</v>
+      </c>
+      <c r="J2011" t="n">
+        <v>499</v>
+      </c>
+      <c r="K2011" t="n">
+        <v>37</v>
+      </c>
+      <c r="L2011" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C2012" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="D2012" t="n">
+        <v>527.03</v>
+      </c>
+      <c r="E2012" t="n">
+        <v>302</v>
+      </c>
+      <c r="F2012" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="G2012" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H2012" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="I2012" t="n">
+        <v>527.03</v>
+      </c>
+      <c r="J2012" t="n">
+        <v>302</v>
+      </c>
+      <c r="K2012" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="L2012" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C2013" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>536.71</v>
+      </c>
+      <c r="E2013" t="n">
+        <v>125</v>
+      </c>
+      <c r="F2013" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G2013" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H2013" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="I2013" t="n">
+        <v>536.71</v>
+      </c>
+      <c r="J2013" t="n">
+        <v>125</v>
+      </c>
+      <c r="K2013" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="L2013" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C2014" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D2014" t="n">
+        <v>537.42</v>
+      </c>
+      <c r="E2014" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2014" t="n">
+        <v>32</v>
+      </c>
+      <c r="G2014" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H2014" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I2014" t="n">
+        <v>537.42</v>
+      </c>
+      <c r="J2014" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2014" t="n">
+        <v>32</v>
+      </c>
+      <c r="L2014" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2015" t="n">
+        <v>537.42</v>
+      </c>
+      <c r="E2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2015" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="G2015" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2015" t="n">
+        <v>537.42</v>
+      </c>
+      <c r="J2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2015" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="L2015" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2016" t="n">
+        <v>537.42</v>
+      </c>
+      <c r="E2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2016" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="G2016" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2016" t="n">
+        <v>537.42</v>
+      </c>
+      <c r="J2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2016" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="L2016" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>537.42</v>
+      </c>
+      <c r="E2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2017" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G2017" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2017" t="n">
+        <v>537.42</v>
+      </c>
+      <c r="J2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2017" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L2017" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/log.xlsx
+++ b/log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2017"/>
+  <dimension ref="A1:L2185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85630,6 +85630,7062 @@
         <v>4.8</v>
       </c>
     </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2018" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2018" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="G2018" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2018" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="L2018" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2019" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2019" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G2019" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2019" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="L2019" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2020" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2020" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G2020" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2020" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="L2020" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2021" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G2021" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2021" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="L2021" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2022" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2022" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G2022" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2022" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="L2022" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2023" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G2023" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2023" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="L2023" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2024" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C2024" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E2024" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2024" t="n">
+        <v>24</v>
+      </c>
+      <c r="G2024" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H2024" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I2024" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J2024" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2024" t="n">
+        <v>24</v>
+      </c>
+      <c r="L2024" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C2025" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="E2025" t="n">
+        <v>103</v>
+      </c>
+      <c r="F2025" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G2025" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H2025" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="I2025" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="J2025" t="n">
+        <v>103</v>
+      </c>
+      <c r="K2025" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="L2025" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C2026" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="D2026" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="E2026" t="n">
+        <v>290</v>
+      </c>
+      <c r="F2026" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G2026" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H2026" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="I2026" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="J2026" t="n">
+        <v>290</v>
+      </c>
+      <c r="K2026" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L2026" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C2027" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="D2027" t="n">
+        <v>67.56999999999999</v>
+      </c>
+      <c r="E2027" t="n">
+        <v>490</v>
+      </c>
+      <c r="F2027" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="G2027" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H2027" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="I2027" t="n">
+        <v>67.56999999999999</v>
+      </c>
+      <c r="J2027" t="n">
+        <v>490</v>
+      </c>
+      <c r="K2027" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="L2027" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C2028" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="D2028" t="n">
+        <v>116.11</v>
+      </c>
+      <c r="E2028" t="n">
+        <v>673</v>
+      </c>
+      <c r="F2028" t="n">
+        <v>33</v>
+      </c>
+      <c r="G2028" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H2028" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="I2028" t="n">
+        <v>116.11</v>
+      </c>
+      <c r="J2028" t="n">
+        <v>673</v>
+      </c>
+      <c r="K2028" t="n">
+        <v>33</v>
+      </c>
+      <c r="L2028" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C2029" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="D2029" t="n">
+        <v>173.2</v>
+      </c>
+      <c r="E2029" t="n">
+        <v>814</v>
+      </c>
+      <c r="F2029" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="G2029" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H2029" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="I2029" t="n">
+        <v>173.2</v>
+      </c>
+      <c r="J2029" t="n">
+        <v>814</v>
+      </c>
+      <c r="K2029" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="L2029" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C2030" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="D2030" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="E2030" t="n">
+        <v>907</v>
+      </c>
+      <c r="F2030" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="G2030" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H2030" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="I2030" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="J2030" t="n">
+        <v>907</v>
+      </c>
+      <c r="K2030" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="L2030" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2031" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C2031" t="n">
+        <v>63.68</v>
+      </c>
+      <c r="D2031" t="n">
+        <v>299.18</v>
+      </c>
+      <c r="E2031" t="n">
+        <v>937</v>
+      </c>
+      <c r="F2031" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G2031" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H2031" t="n">
+        <v>63.68</v>
+      </c>
+      <c r="I2031" t="n">
+        <v>299.18</v>
+      </c>
+      <c r="J2031" t="n">
+        <v>937</v>
+      </c>
+      <c r="K2031" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L2031" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2032" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C2032" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="D2032" t="n">
+        <v>361.04</v>
+      </c>
+      <c r="E2032" t="n">
+        <v>911</v>
+      </c>
+      <c r="F2032" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="G2032" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H2032" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="I2032" t="n">
+        <v>361.04</v>
+      </c>
+      <c r="J2032" t="n">
+        <v>911</v>
+      </c>
+      <c r="K2032" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="L2032" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C2033" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="D2033" t="n">
+        <v>417.59</v>
+      </c>
+      <c r="E2033" t="n">
+        <v>821</v>
+      </c>
+      <c r="F2033" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="G2033" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H2033" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="I2033" t="n">
+        <v>417.59</v>
+      </c>
+      <c r="J2033" t="n">
+        <v>821</v>
+      </c>
+      <c r="K2033" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="L2033" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2034" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C2034" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="D2034" t="n">
+        <v>466.19</v>
+      </c>
+      <c r="E2034" t="n">
+        <v>687</v>
+      </c>
+      <c r="F2034" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="G2034" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H2034" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="I2034" t="n">
+        <v>466.19</v>
+      </c>
+      <c r="J2034" t="n">
+        <v>687</v>
+      </c>
+      <c r="K2034" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="L2034" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2035" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C2035" t="n">
+        <v>36.91</v>
+      </c>
+      <c r="D2035" t="n">
+        <v>503.1</v>
+      </c>
+      <c r="E2035" t="n">
+        <v>506</v>
+      </c>
+      <c r="F2035" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="G2035" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H2035" t="n">
+        <v>36.91</v>
+      </c>
+      <c r="I2035" t="n">
+        <v>503.1</v>
+      </c>
+      <c r="J2035" t="n">
+        <v>506</v>
+      </c>
+      <c r="K2035" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="L2035" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2036" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C2036" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="D2036" t="n">
+        <v>526.66</v>
+      </c>
+      <c r="E2036" t="n">
+        <v>312</v>
+      </c>
+      <c r="F2036" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="G2036" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H2036" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="I2036" t="n">
+        <v>526.66</v>
+      </c>
+      <c r="J2036" t="n">
+        <v>312</v>
+      </c>
+      <c r="K2036" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="L2036" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2037" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C2037" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="D2037" t="n">
+        <v>536.1</v>
+      </c>
+      <c r="E2037" t="n">
+        <v>121</v>
+      </c>
+      <c r="F2037" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="G2037" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2037" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="I2037" t="n">
+        <v>536.1</v>
+      </c>
+      <c r="J2037" t="n">
+        <v>121</v>
+      </c>
+      <c r="K2037" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="L2037" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2038" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C2038" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D2038" t="n">
+        <v>536.74</v>
+      </c>
+      <c r="E2038" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2038" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G2038" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H2038" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I2038" t="n">
+        <v>536.74</v>
+      </c>
+      <c r="J2038" t="n">
+        <v>8</v>
+      </c>
+      <c r="K2038" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="L2038" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2039" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C2039" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2039" t="n">
+        <v>536.74</v>
+      </c>
+      <c r="E2039" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2039" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="G2039" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H2039" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2039" t="n">
+        <v>536.74</v>
+      </c>
+      <c r="J2039" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2039" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="L2039" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2040" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C2040" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2040" t="n">
+        <v>536.74</v>
+      </c>
+      <c r="E2040" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2040" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="G2040" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H2040" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2040" t="n">
+        <v>536.74</v>
+      </c>
+      <c r="J2040" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2040" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="L2040" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B2041" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C2041" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2041" t="n">
+        <v>536.74</v>
+      </c>
+      <c r="E2041" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2041" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2041" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H2041" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2041" t="n">
+        <v>536.74</v>
+      </c>
+      <c r="J2041" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2041" t="n">
+        <v>30</v>
+      </c>
+      <c r="L2041" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2042" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2042" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G2042" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2042" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2042" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="L2042" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2043" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2043" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="G2043" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2043" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2043" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="L2043" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2044" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2044" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="G2044" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2044" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2044" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="L2044" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2045" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C2045" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2045" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2045" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2045" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G2045" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H2045" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2045" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2045" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2045" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="L2045" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2046" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2046" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G2046" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2046" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2046" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="L2046" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2047" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2047" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G2047" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2047" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2047" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="L2047" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2048" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C2048" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D2048" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E2048" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2048" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G2048" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H2048" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I2048" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J2048" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2048" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="L2048" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2049" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C2049" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="D2049" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="E2049" t="n">
+        <v>99</v>
+      </c>
+      <c r="F2049" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="G2049" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H2049" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="I2049" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="J2049" t="n">
+        <v>99</v>
+      </c>
+      <c r="K2049" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="L2049" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2050" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C2050" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="D2050" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E2050" t="n">
+        <v>283</v>
+      </c>
+      <c r="F2050" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="G2050" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H2050" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="I2050" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="J2050" t="n">
+        <v>283</v>
+      </c>
+      <c r="K2050" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="L2050" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2051" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C2051" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="D2051" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="E2051" t="n">
+        <v>481</v>
+      </c>
+      <c r="F2051" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="G2051" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H2051" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="I2051" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="J2051" t="n">
+        <v>481</v>
+      </c>
+      <c r="K2051" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="L2051" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2052" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C2052" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="D2052" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="E2052" t="n">
+        <v>661</v>
+      </c>
+      <c r="F2052" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="G2052" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H2052" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="I2052" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="J2052" t="n">
+        <v>661</v>
+      </c>
+      <c r="K2052" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="L2052" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2053" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C2053" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="D2053" t="n">
+        <v>169.55</v>
+      </c>
+      <c r="E2053" t="n">
+        <v>803</v>
+      </c>
+      <c r="F2053" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="G2053" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H2053" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="I2053" t="n">
+        <v>169.55</v>
+      </c>
+      <c r="J2053" t="n">
+        <v>803</v>
+      </c>
+      <c r="K2053" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="L2053" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2054" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C2054" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="D2054" t="n">
+        <v>231.08</v>
+      </c>
+      <c r="E2054" t="n">
+        <v>892</v>
+      </c>
+      <c r="F2054" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="G2054" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H2054" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="I2054" t="n">
+        <v>231.08</v>
+      </c>
+      <c r="J2054" t="n">
+        <v>892</v>
+      </c>
+      <c r="K2054" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="L2054" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2055" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C2055" t="n">
+        <v>61.92</v>
+      </c>
+      <c r="D2055" t="n">
+        <v>293</v>
+      </c>
+      <c r="E2055" t="n">
+        <v>898</v>
+      </c>
+      <c r="F2055" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="G2055" t="n">
+        <v>13</v>
+      </c>
+      <c r="H2055" t="n">
+        <v>61.92</v>
+      </c>
+      <c r="I2055" t="n">
+        <v>293</v>
+      </c>
+      <c r="J2055" t="n">
+        <v>898</v>
+      </c>
+      <c r="K2055" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="L2055" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2056" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C2056" t="n">
+        <v>60.82</v>
+      </c>
+      <c r="D2056" t="n">
+        <v>353.82</v>
+      </c>
+      <c r="E2056" t="n">
+        <v>875</v>
+      </c>
+      <c r="F2056" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="G2056" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H2056" t="n">
+        <v>60.82</v>
+      </c>
+      <c r="I2056" t="n">
+        <v>353.82</v>
+      </c>
+      <c r="J2056" t="n">
+        <v>875</v>
+      </c>
+      <c r="K2056" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="L2056" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2057" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C2057" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="D2057" t="n">
+        <v>409.32</v>
+      </c>
+      <c r="E2057" t="n">
+        <v>788</v>
+      </c>
+      <c r="F2057" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G2057" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H2057" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="I2057" t="n">
+        <v>409.32</v>
+      </c>
+      <c r="J2057" t="n">
+        <v>788</v>
+      </c>
+      <c r="K2057" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="L2057" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2058" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C2058" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="D2058" t="n">
+        <v>455.26</v>
+      </c>
+      <c r="E2058" t="n">
+        <v>634</v>
+      </c>
+      <c r="F2058" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="G2058" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H2058" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="I2058" t="n">
+        <v>455.26</v>
+      </c>
+      <c r="J2058" t="n">
+        <v>634</v>
+      </c>
+      <c r="K2058" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="L2058" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2059" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C2059" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="D2059" t="n">
+        <v>488.11</v>
+      </c>
+      <c r="E2059" t="n">
+        <v>439</v>
+      </c>
+      <c r="F2059" t="n">
+        <v>32</v>
+      </c>
+      <c r="G2059" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H2059" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="I2059" t="n">
+        <v>488.11</v>
+      </c>
+      <c r="J2059" t="n">
+        <v>439</v>
+      </c>
+      <c r="K2059" t="n">
+        <v>32</v>
+      </c>
+      <c r="L2059" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2060" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C2060" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="D2060" t="n">
+        <v>510.38</v>
+      </c>
+      <c r="E2060" t="n">
+        <v>289</v>
+      </c>
+      <c r="F2060" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G2060" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H2060" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="I2060" t="n">
+        <v>510.38</v>
+      </c>
+      <c r="J2060" t="n">
+        <v>289</v>
+      </c>
+      <c r="K2060" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="L2060" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2061" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C2061" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="D2061" t="n">
+        <v>519.41</v>
+      </c>
+      <c r="E2061" t="n">
+        <v>114</v>
+      </c>
+      <c r="F2061" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G2061" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2061" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="I2061" t="n">
+        <v>519.41</v>
+      </c>
+      <c r="J2061" t="n">
+        <v>114</v>
+      </c>
+      <c r="K2061" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L2061" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2062" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C2062" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D2062" t="n">
+        <v>519.97</v>
+      </c>
+      <c r="E2062" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2062" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="G2062" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H2062" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I2062" t="n">
+        <v>519.97</v>
+      </c>
+      <c r="J2062" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2062" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="L2062" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2063" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2063" t="n">
+        <v>519.97</v>
+      </c>
+      <c r="E2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2063" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G2063" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2063" t="n">
+        <v>519.97</v>
+      </c>
+      <c r="J2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2063" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="L2063" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2064" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C2064" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2064" t="n">
+        <v>519.97</v>
+      </c>
+      <c r="E2064" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2064" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="G2064" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H2064" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2064" t="n">
+        <v>519.97</v>
+      </c>
+      <c r="J2064" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2064" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="L2064" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B2065" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2065" t="n">
+        <v>519.97</v>
+      </c>
+      <c r="E2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2065" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="G2065" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2065" t="n">
+        <v>519.97</v>
+      </c>
+      <c r="J2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2065" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="L2065" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2066" t="n">
+        <v>27</v>
+      </c>
+      <c r="G2066" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2066" t="n">
+        <v>27</v>
+      </c>
+      <c r="L2066" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C2067" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2067" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2067" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2067" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G2067" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H2067" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2067" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2067" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2067" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="L2067" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C2068" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2068" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2068" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2068" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G2068" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H2068" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2068" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2068" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2068" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="L2068" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C2069" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2069" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2069" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2069" t="n">
+        <v>26</v>
+      </c>
+      <c r="G2069" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H2069" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2069" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2069" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2069" t="n">
+        <v>26</v>
+      </c>
+      <c r="L2069" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2070" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="G2070" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2070" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="L2070" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C2071" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2071" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2071" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2071" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2071" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2071" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2071" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2071" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2071" t="n">
+        <v>25</v>
+      </c>
+      <c r="L2071" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2072" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C2072" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D2072" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E2072" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2072" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G2072" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2072" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I2072" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J2072" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2072" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="L2072" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C2073" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="D2073" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="E2073" t="n">
+        <v>89</v>
+      </c>
+      <c r="F2073" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G2073" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H2073" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="I2073" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="J2073" t="n">
+        <v>89</v>
+      </c>
+      <c r="K2073" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="L2073" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2074" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C2074" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="D2074" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="E2074" t="n">
+        <v>268</v>
+      </c>
+      <c r="F2074" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G2074" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H2074" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="I2074" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="J2074" t="n">
+        <v>268</v>
+      </c>
+      <c r="K2074" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L2074" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C2075" t="n">
+        <v>34.63</v>
+      </c>
+      <c r="D2075" t="n">
+        <v>62.81</v>
+      </c>
+      <c r="E2075" t="n">
+        <v>463</v>
+      </c>
+      <c r="F2075" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="G2075" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H2075" t="n">
+        <v>34.63</v>
+      </c>
+      <c r="I2075" t="n">
+        <v>62.81</v>
+      </c>
+      <c r="J2075" t="n">
+        <v>463</v>
+      </c>
+      <c r="K2075" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="L2075" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2076" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C2076" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D2076" t="n">
+        <v>107.18</v>
+      </c>
+      <c r="E2076" t="n">
+        <v>608</v>
+      </c>
+      <c r="F2076" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="G2076" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H2076" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="I2076" t="n">
+        <v>107.18</v>
+      </c>
+      <c r="J2076" t="n">
+        <v>608</v>
+      </c>
+      <c r="K2076" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="L2076" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C2077" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="D2077" t="n">
+        <v>158.88</v>
+      </c>
+      <c r="E2077" t="n">
+        <v>724</v>
+      </c>
+      <c r="F2077" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G2077" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H2077" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="I2077" t="n">
+        <v>158.88</v>
+      </c>
+      <c r="J2077" t="n">
+        <v>724</v>
+      </c>
+      <c r="K2077" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="L2077" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2078" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C2078" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>214.75</v>
+      </c>
+      <c r="E2078" t="n">
+        <v>794</v>
+      </c>
+      <c r="F2078" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G2078" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H2078" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="I2078" t="n">
+        <v>214.75</v>
+      </c>
+      <c r="J2078" t="n">
+        <v>794</v>
+      </c>
+      <c r="K2078" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="L2078" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2079" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C2079" t="n">
+        <v>58.52</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>273.27</v>
+      </c>
+      <c r="E2079" t="n">
+        <v>835</v>
+      </c>
+      <c r="F2079" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="G2079" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H2079" t="n">
+        <v>58.52</v>
+      </c>
+      <c r="I2079" t="n">
+        <v>273.27</v>
+      </c>
+      <c r="J2079" t="n">
+        <v>835</v>
+      </c>
+      <c r="K2079" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="L2079" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2080" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C2080" t="n">
+        <v>56.41</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>329.68</v>
+      </c>
+      <c r="E2080" t="n">
+        <v>787</v>
+      </c>
+      <c r="F2080" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="G2080" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H2080" t="n">
+        <v>56.41</v>
+      </c>
+      <c r="I2080" t="n">
+        <v>329.68</v>
+      </c>
+      <c r="J2080" t="n">
+        <v>787</v>
+      </c>
+      <c r="K2080" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="L2080" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C2081" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>381.85</v>
+      </c>
+      <c r="E2081" t="n">
+        <v>720</v>
+      </c>
+      <c r="F2081" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="G2081" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H2081" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="I2081" t="n">
+        <v>381.85</v>
+      </c>
+      <c r="J2081" t="n">
+        <v>720</v>
+      </c>
+      <c r="K2081" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="L2081" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2082" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C2082" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>425.53</v>
+      </c>
+      <c r="E2082" t="n">
+        <v>591</v>
+      </c>
+      <c r="F2082" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="G2082" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H2082" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="I2082" t="n">
+        <v>425.53</v>
+      </c>
+      <c r="J2082" t="n">
+        <v>591</v>
+      </c>
+      <c r="K2082" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="L2082" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C2083" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>460.12</v>
+      </c>
+      <c r="E2083" t="n">
+        <v>461</v>
+      </c>
+      <c r="F2083" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="G2083" t="n">
+        <v>11</v>
+      </c>
+      <c r="H2083" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="I2083" t="n">
+        <v>460.12</v>
+      </c>
+      <c r="J2083" t="n">
+        <v>461</v>
+      </c>
+      <c r="K2083" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="L2083" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C2084" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>480.31</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>261</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="G2084" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H2084" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="I2084" t="n">
+        <v>480.31</v>
+      </c>
+      <c r="J2084" t="n">
+        <v>261</v>
+      </c>
+      <c r="K2084" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="L2084" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C2085" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>488.39</v>
+      </c>
+      <c r="E2085" t="n">
+        <v>102</v>
+      </c>
+      <c r="F2085" t="n">
+        <v>29</v>
+      </c>
+      <c r="G2085" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2085" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="I2085" t="n">
+        <v>488.39</v>
+      </c>
+      <c r="J2085" t="n">
+        <v>102</v>
+      </c>
+      <c r="K2085" t="n">
+        <v>29</v>
+      </c>
+      <c r="L2085" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2086" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C2086" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>488.79</v>
+      </c>
+      <c r="E2086" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2086" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="G2086" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H2086" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I2086" t="n">
+        <v>488.79</v>
+      </c>
+      <c r="J2086" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2086" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="L2086" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>488.79</v>
+      </c>
+      <c r="E2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2087" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="G2087" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2087" t="n">
+        <v>488.79</v>
+      </c>
+      <c r="J2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2087" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="L2087" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2088" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>488.79</v>
+      </c>
+      <c r="E2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2088" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="G2088" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2088" t="n">
+        <v>488.79</v>
+      </c>
+      <c r="J2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2088" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="L2088" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>488.79</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G2089" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2089" t="n">
+        <v>488.79</v>
+      </c>
+      <c r="J2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2089" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="L2089" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2090" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="G2090" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2090" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="L2090" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G2091" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2091" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="L2091" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2092" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2092" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G2092" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2092" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="L2092" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2093" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G2093" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2093" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="L2093" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2094" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2094" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2094" t="n">
+        <v>25</v>
+      </c>
+      <c r="L2094" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2095" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G2095" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2095" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="L2095" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2096" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C2096" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E2096" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2096" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G2096" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H2096" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I2096" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J2096" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2096" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="L2096" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C2097" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="E2097" t="n">
+        <v>87</v>
+      </c>
+      <c r="F2097" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G2097" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H2097" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="I2097" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="J2097" t="n">
+        <v>87</v>
+      </c>
+      <c r="K2097" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="L2097" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2098" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C2098" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>255</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="G2098" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H2098" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="I2098" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="J2098" t="n">
+        <v>255</v>
+      </c>
+      <c r="K2098" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="L2098" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2099" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C2099" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>59.83</v>
+      </c>
+      <c r="E2099" t="n">
+        <v>434</v>
+      </c>
+      <c r="F2099" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="G2099" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2099" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="I2099" t="n">
+        <v>59.83</v>
+      </c>
+      <c r="J2099" t="n">
+        <v>434</v>
+      </c>
+      <c r="K2099" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="L2099" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2100" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C2100" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>104.11</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>603</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="G2100" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H2100" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="I2100" t="n">
+        <v>104.11</v>
+      </c>
+      <c r="J2100" t="n">
+        <v>603</v>
+      </c>
+      <c r="K2100" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="L2100" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C2101" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>156.19</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>724</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>32</v>
+      </c>
+      <c r="G2101" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H2101" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="I2101" t="n">
+        <v>156.19</v>
+      </c>
+      <c r="J2101" t="n">
+        <v>724</v>
+      </c>
+      <c r="K2101" t="n">
+        <v>32</v>
+      </c>
+      <c r="L2101" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C2102" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>214.06</v>
+      </c>
+      <c r="E2102" t="n">
+        <v>818</v>
+      </c>
+      <c r="F2102" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="G2102" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H2102" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="I2102" t="n">
+        <v>214.06</v>
+      </c>
+      <c r="J2102" t="n">
+        <v>818</v>
+      </c>
+      <c r="K2102" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="L2102" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C2103" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>274.6</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>858</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>32</v>
+      </c>
+      <c r="G2103" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2103" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="I2103" t="n">
+        <v>274.6</v>
+      </c>
+      <c r="J2103" t="n">
+        <v>858</v>
+      </c>
+      <c r="K2103" t="n">
+        <v>32</v>
+      </c>
+      <c r="L2103" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C2104" t="n">
+        <v>59.77</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>334.37</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>845</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="G2104" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H2104" t="n">
+        <v>59.77</v>
+      </c>
+      <c r="I2104" t="n">
+        <v>334.37</v>
+      </c>
+      <c r="J2104" t="n">
+        <v>845</v>
+      </c>
+      <c r="K2104" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="L2104" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C2105" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>388.05</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>750</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H2105" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="I2105" t="n">
+        <v>388.05</v>
+      </c>
+      <c r="J2105" t="n">
+        <v>750</v>
+      </c>
+      <c r="K2105" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="L2105" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C2106" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>432.35</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>604</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="G2106" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H2106" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="I2106" t="n">
+        <v>432.35</v>
+      </c>
+      <c r="J2106" t="n">
+        <v>604</v>
+      </c>
+      <c r="K2106" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="L2106" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C2107" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>466.88</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>459</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="G2107" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H2107" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="I2107" t="n">
+        <v>466.88</v>
+      </c>
+      <c r="J2107" t="n">
+        <v>459</v>
+      </c>
+      <c r="K2107" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="L2107" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C2108" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>488.33</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>277</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H2108" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="I2108" t="n">
+        <v>488.33</v>
+      </c>
+      <c r="J2108" t="n">
+        <v>277</v>
+      </c>
+      <c r="K2108" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="L2108" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C2109" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>496.82</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>107</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G2109" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H2109" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="I2109" t="n">
+        <v>496.82</v>
+      </c>
+      <c r="J2109" t="n">
+        <v>107</v>
+      </c>
+      <c r="K2109" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="L2109" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C2110" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>497.3</v>
+      </c>
+      <c r="E2110" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2110" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="G2110" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H2110" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I2110" t="n">
+        <v>497.3</v>
+      </c>
+      <c r="J2110" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2110" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="L2110" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>497.3</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G2111" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2111" t="n">
+        <v>497.3</v>
+      </c>
+      <c r="J2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2111" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="L2111" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>497.3</v>
+      </c>
+      <c r="E2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2112" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G2112" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2112" t="n">
+        <v>497.3</v>
+      </c>
+      <c r="J2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2112" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="L2112" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>497.3</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G2113" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2113" t="n">
+        <v>497.3</v>
+      </c>
+      <c r="J2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2113" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="L2113" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G2114" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2114" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="L2114" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2115" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2115" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2115" t="n">
+        <v>25</v>
+      </c>
+      <c r="L2115" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2116" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G2116" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2116" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="L2116" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2117" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G2117" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2117" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="L2117" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2118" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G2118" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2118" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="L2118" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2119" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G2119" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2119" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="L2119" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C2120" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E2120" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2120" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G2120" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2120" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I2120" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J2120" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2120" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="L2120" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C2121" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="E2121" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2121" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G2121" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H2121" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="I2121" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="J2121" t="n">
+        <v>90</v>
+      </c>
+      <c r="K2121" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="L2121" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C2122" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="E2122" t="n">
+        <v>272</v>
+      </c>
+      <c r="F2122" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="G2122" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H2122" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="I2122" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="J2122" t="n">
+        <v>272</v>
+      </c>
+      <c r="K2122" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="L2122" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C2123" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>64.11</v>
+      </c>
+      <c r="E2123" t="n">
+        <v>471</v>
+      </c>
+      <c r="F2123" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="G2123" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H2123" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="I2123" t="n">
+        <v>64.11</v>
+      </c>
+      <c r="J2123" t="n">
+        <v>471</v>
+      </c>
+      <c r="K2123" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="L2123" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2124" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C2124" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>111.68</v>
+      </c>
+      <c r="E2124" t="n">
+        <v>652</v>
+      </c>
+      <c r="F2124" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G2124" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H2124" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="I2124" t="n">
+        <v>111.68</v>
+      </c>
+      <c r="J2124" t="n">
+        <v>652</v>
+      </c>
+      <c r="K2124" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="L2124" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C2125" t="n">
+        <v>56.29</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>167.97</v>
+      </c>
+      <c r="E2125" t="n">
+        <v>794</v>
+      </c>
+      <c r="F2125" t="n">
+        <v>33</v>
+      </c>
+      <c r="G2125" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H2125" t="n">
+        <v>56.29</v>
+      </c>
+      <c r="I2125" t="n">
+        <v>167.97</v>
+      </c>
+      <c r="J2125" t="n">
+        <v>794</v>
+      </c>
+      <c r="K2125" t="n">
+        <v>33</v>
+      </c>
+      <c r="L2125" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2126" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C2126" t="n">
+        <v>61.09</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>229.06</v>
+      </c>
+      <c r="E2126" t="n">
+        <v>879</v>
+      </c>
+      <c r="F2126" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G2126" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H2126" t="n">
+        <v>61.09</v>
+      </c>
+      <c r="I2126" t="n">
+        <v>229.06</v>
+      </c>
+      <c r="J2126" t="n">
+        <v>879</v>
+      </c>
+      <c r="K2126" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="L2126" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C2127" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>286.57</v>
+      </c>
+      <c r="E2127" t="n">
+        <v>817</v>
+      </c>
+      <c r="F2127" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G2127" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H2127" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="I2127" t="n">
+        <v>286.57</v>
+      </c>
+      <c r="J2127" t="n">
+        <v>817</v>
+      </c>
+      <c r="K2127" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="L2127" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2128" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C2128" t="n">
+        <v>55.81</v>
+      </c>
+      <c r="D2128" t="n">
+        <v>342.38</v>
+      </c>
+      <c r="E2128" t="n">
+        <v>791</v>
+      </c>
+      <c r="F2128" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="G2128" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H2128" t="n">
+        <v>55.81</v>
+      </c>
+      <c r="I2128" t="n">
+        <v>342.38</v>
+      </c>
+      <c r="J2128" t="n">
+        <v>791</v>
+      </c>
+      <c r="K2128" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="L2128" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C2129" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="D2129" t="n">
+        <v>397.85</v>
+      </c>
+      <c r="E2129" t="n">
+        <v>781</v>
+      </c>
+      <c r="F2129" t="n">
+        <v>33</v>
+      </c>
+      <c r="G2129" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H2129" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="I2129" t="n">
+        <v>397.85</v>
+      </c>
+      <c r="J2129" t="n">
+        <v>781</v>
+      </c>
+      <c r="K2129" t="n">
+        <v>33</v>
+      </c>
+      <c r="L2129" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C2130" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="D2130" t="n">
+        <v>444.66</v>
+      </c>
+      <c r="E2130" t="n">
+        <v>645</v>
+      </c>
+      <c r="F2130" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="G2130" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H2130" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="I2130" t="n">
+        <v>444.66</v>
+      </c>
+      <c r="J2130" t="n">
+        <v>645</v>
+      </c>
+      <c r="K2130" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="L2130" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C2131" t="n">
+        <v>37.16</v>
+      </c>
+      <c r="D2131" t="n">
+        <v>481.82</v>
+      </c>
+      <c r="E2131" t="n">
+        <v>501</v>
+      </c>
+      <c r="F2131" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="G2131" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H2131" t="n">
+        <v>37.16</v>
+      </c>
+      <c r="I2131" t="n">
+        <v>481.82</v>
+      </c>
+      <c r="J2131" t="n">
+        <v>501</v>
+      </c>
+      <c r="K2131" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="L2131" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C2132" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="D2132" t="n">
+        <v>504.77</v>
+      </c>
+      <c r="E2132" t="n">
+        <v>300</v>
+      </c>
+      <c r="F2132" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="G2132" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H2132" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="I2132" t="n">
+        <v>504.77</v>
+      </c>
+      <c r="J2132" t="n">
+        <v>300</v>
+      </c>
+      <c r="K2132" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="L2132" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C2133" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="D2133" t="n">
+        <v>513.61</v>
+      </c>
+      <c r="E2133" t="n">
+        <v>112</v>
+      </c>
+      <c r="F2133" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="G2133" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H2133" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="I2133" t="n">
+        <v>513.61</v>
+      </c>
+      <c r="J2133" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2133" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="L2133" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C2134" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D2134" t="n">
+        <v>514.09</v>
+      </c>
+      <c r="E2134" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2134" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="G2134" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2134" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I2134" t="n">
+        <v>514.09</v>
+      </c>
+      <c r="J2134" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2134" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="L2134" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C2135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2135" t="n">
+        <v>514.09</v>
+      </c>
+      <c r="E2135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2135" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="G2135" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H2135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2135" t="n">
+        <v>514.09</v>
+      </c>
+      <c r="J2135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2135" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="L2135" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C2136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2136" t="n">
+        <v>514.09</v>
+      </c>
+      <c r="E2136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2136" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="G2136" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H2136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2136" t="n">
+        <v>514.09</v>
+      </c>
+      <c r="J2136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2136" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="L2136" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C2137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2137" t="n">
+        <v>514.09</v>
+      </c>
+      <c r="E2137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2137" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G2137" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H2137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2137" t="n">
+        <v>514.09</v>
+      </c>
+      <c r="J2137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2137" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="L2137" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C2138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C2139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C2140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C2141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C2143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C2145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C2148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C2149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C2150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C2151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C2152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C2153" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C2154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C2155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C2156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C2157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C2158" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2158" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C2159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C2160" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C2161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>0시</t>
+        </is>
+      </c>
+      <c r="C2162" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2162" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G2162" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H2162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2162" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="L2162" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>1시</t>
+        </is>
+      </c>
+      <c r="C2163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2163" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G2163" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H2163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2163" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="L2163" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>2시</t>
+        </is>
+      </c>
+      <c r="C2164" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2164" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G2164" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H2164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2164" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="L2164" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>3시</t>
+        </is>
+      </c>
+      <c r="C2165" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2165" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G2165" t="n">
+        <v>15</v>
+      </c>
+      <c r="H2165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2165" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="L2165" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>4시</t>
+        </is>
+      </c>
+      <c r="C2166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2166" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G2166" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H2166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2166" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="L2166" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>5시</t>
+        </is>
+      </c>
+      <c r="C2167" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2167" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G2167" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H2167" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2167" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="L2167" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>6시</t>
+        </is>
+      </c>
+      <c r="C2168" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D2168" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E2168" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2168" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G2168" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H2168" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I2168" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J2168" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2168" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="L2168" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>7시</t>
+        </is>
+      </c>
+      <c r="C2169" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D2169" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="E2169" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2169" t="n">
+        <v>23</v>
+      </c>
+      <c r="G2169" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H2169" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I2169" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="J2169" t="n">
+        <v>30</v>
+      </c>
+      <c r="K2169" t="n">
+        <v>23</v>
+      </c>
+      <c r="L2169" t="n">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>8시</t>
+        </is>
+      </c>
+      <c r="C2170" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="D2170" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="E2170" t="n">
+        <v>79</v>
+      </c>
+      <c r="F2170" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G2170" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2170" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="I2170" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="J2170" t="n">
+        <v>79</v>
+      </c>
+      <c r="K2170" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="L2170" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>9시</t>
+        </is>
+      </c>
+      <c r="C2171" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="D2171" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="E2171" t="n">
+        <v>189</v>
+      </c>
+      <c r="F2171" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G2171" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H2171" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="I2171" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="J2171" t="n">
+        <v>189</v>
+      </c>
+      <c r="K2171" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="L2171" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>10시</t>
+        </is>
+      </c>
+      <c r="C2172" t="n">
+        <v>28</v>
+      </c>
+      <c r="D2172" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="E2172" t="n">
+        <v>363</v>
+      </c>
+      <c r="F2172" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="G2172" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H2172" t="n">
+        <v>28</v>
+      </c>
+      <c r="I2172" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="J2172" t="n">
+        <v>363</v>
+      </c>
+      <c r="K2172" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="L2172" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>11시</t>
+        </is>
+      </c>
+      <c r="C2173" t="n">
+        <v>38.94</v>
+      </c>
+      <c r="D2173" t="n">
+        <v>90.87</v>
+      </c>
+      <c r="E2173" t="n">
+        <v>519</v>
+      </c>
+      <c r="F2173" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G2173" t="n">
+        <v>21</v>
+      </c>
+      <c r="H2173" t="n">
+        <v>38.94</v>
+      </c>
+      <c r="I2173" t="n">
+        <v>90.87</v>
+      </c>
+      <c r="J2173" t="n">
+        <v>519</v>
+      </c>
+      <c r="K2173" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="L2173" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>12시</t>
+        </is>
+      </c>
+      <c r="C2174" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="D2174" t="n">
+        <v>135.16</v>
+      </c>
+      <c r="E2174" t="n">
+        <v>600</v>
+      </c>
+      <c r="F2174" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="G2174" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H2174" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="I2174" t="n">
+        <v>135.16</v>
+      </c>
+      <c r="J2174" t="n">
+        <v>600</v>
+      </c>
+      <c r="K2174" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="L2174" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>13시</t>
+        </is>
+      </c>
+      <c r="C2175" t="n">
+        <v>53.28</v>
+      </c>
+      <c r="D2175" t="n">
+        <v>188.44</v>
+      </c>
+      <c r="E2175" t="n">
+        <v>740</v>
+      </c>
+      <c r="F2175" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="G2175" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H2175" t="n">
+        <v>53.28</v>
+      </c>
+      <c r="I2175" t="n">
+        <v>188.44</v>
+      </c>
+      <c r="J2175" t="n">
+        <v>740</v>
+      </c>
+      <c r="K2175" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="L2175" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>14시</t>
+        </is>
+      </c>
+      <c r="C2176" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="D2176" t="n">
+        <v>232.1</v>
+      </c>
+      <c r="E2176" t="n">
+        <v>593</v>
+      </c>
+      <c r="F2176" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="G2176" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H2176" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="I2176" t="n">
+        <v>232.1</v>
+      </c>
+      <c r="J2176" t="n">
+        <v>593</v>
+      </c>
+      <c r="K2176" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="L2176" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>15시</t>
+        </is>
+      </c>
+      <c r="C2177" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="D2177" t="n">
+        <v>264.19</v>
+      </c>
+      <c r="E2177" t="n">
+        <v>426</v>
+      </c>
+      <c r="F2177" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="G2177" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H2177" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="I2177" t="n">
+        <v>264.19</v>
+      </c>
+      <c r="J2177" t="n">
+        <v>426</v>
+      </c>
+      <c r="K2177" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="L2177" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>16시</t>
+        </is>
+      </c>
+      <c r="C2178" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="D2178" t="n">
+        <v>294.99</v>
+      </c>
+      <c r="E2178" t="n">
+        <v>407</v>
+      </c>
+      <c r="F2178" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="G2178" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H2178" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I2178" t="n">
+        <v>294.99</v>
+      </c>
+      <c r="J2178" t="n">
+        <v>407</v>
+      </c>
+      <c r="K2178" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="L2178" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>17시</t>
+        </is>
+      </c>
+      <c r="C2179" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="D2179" t="n">
+        <v>321.95</v>
+      </c>
+      <c r="E2179" t="n">
+        <v>353</v>
+      </c>
+      <c r="F2179" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2179" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H2179" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="I2179" t="n">
+        <v>321.95</v>
+      </c>
+      <c r="J2179" t="n">
+        <v>353</v>
+      </c>
+      <c r="K2179" t="n">
+        <v>30</v>
+      </c>
+      <c r="L2179" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>18시</t>
+        </is>
+      </c>
+      <c r="C2180" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="D2180" t="n">
+        <v>337.76</v>
+      </c>
+      <c r="E2180" t="n">
+        <v>202</v>
+      </c>
+      <c r="F2180" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G2180" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H2180" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="I2180" t="n">
+        <v>337.76</v>
+      </c>
+      <c r="J2180" t="n">
+        <v>202</v>
+      </c>
+      <c r="K2180" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="L2180" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>19시</t>
+        </is>
+      </c>
+      <c r="C2181" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="D2181" t="n">
+        <v>343.45</v>
+      </c>
+      <c r="E2181" t="n">
+        <v>71</v>
+      </c>
+      <c r="F2181" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="G2181" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H2181" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="I2181" t="n">
+        <v>343.45</v>
+      </c>
+      <c r="J2181" t="n">
+        <v>71</v>
+      </c>
+      <c r="K2181" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="L2181" t="n">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2182" t="inlineStr">
+        <is>
+          <t>20시</t>
+        </is>
+      </c>
+      <c r="C2182" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D2182" t="n">
+        <v>343.69</v>
+      </c>
+      <c r="E2182" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2182" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G2182" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H2182" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I2182" t="n">
+        <v>343.69</v>
+      </c>
+      <c r="J2182" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2182" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="L2182" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2183" t="inlineStr">
+        <is>
+          <t>21시</t>
+        </is>
+      </c>
+      <c r="C2183" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2183" t="n">
+        <v>343.69</v>
+      </c>
+      <c r="E2183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2183" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2183" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H2183" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2183" t="n">
+        <v>343.69</v>
+      </c>
+      <c r="J2183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2183" t="n">
+        <v>25</v>
+      </c>
+      <c r="L2183" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>22시</t>
+        </is>
+      </c>
+      <c r="C2184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2184" t="n">
+        <v>343.69</v>
+      </c>
+      <c r="E2184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2184" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G2184" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H2184" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2184" t="n">
+        <v>343.69</v>
+      </c>
+      <c r="J2184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2184" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="L2184" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>23시</t>
+        </is>
+      </c>
+      <c r="C2185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2185" t="n">
+        <v>343.69</v>
+      </c>
+      <c r="E2185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2185" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G2185" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H2185" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2185" t="n">
+        <v>343.69</v>
+      </c>
+      <c r="J2185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2185" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="L2185" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
